--- a/reports/Debug-purgatory-20260104/purgatory_Report_20260104.xlsx
+++ b/reports/Debug-purgatory-20260104/purgatory_Report_20260104.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>purgatory Resort
 Daily Management Report
@@ -103,6 +103,15 @@
     <t>FINANCIALS</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Payroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR % of </t>
+  </si>
+  <si>
     <t>Mountain G&amp;A - Revenue</t>
   </si>
   <si>
@@ -220,6 +229,15 @@
     <t>PR % of Rentals</t>
   </si>
   <si>
+    <t>The Board Room - Revenue</t>
+  </si>
+  <si>
+    <t>The Board Room - Payroll</t>
+  </si>
+  <si>
+    <t>PR % of The Board Room</t>
+  </si>
+  <si>
     <t>Expert Edge - Revenue</t>
   </si>
   <si>
@@ -472,6 +490,15 @@
     <t>PR % of Transportation</t>
   </si>
   <si>
+    <t>Commercial Tenants - Revenue</t>
+  </si>
+  <si>
+    <t>Commercial Tenants - Payroll</t>
+  </si>
+  <si>
+    <t>PR % of Commercial Tenants</t>
+  </si>
+  <si>
     <t>D7000 - Revenue</t>
   </si>
   <si>
@@ -488,6 +515,15 @@
   </si>
   <si>
     <t>PR % of Marketing</t>
+  </si>
+  <si>
+    <t>General Administration - Revenue</t>
+  </si>
+  <si>
+    <t>General Administration - Payroll</t>
+  </si>
+  <si>
+    <t>PR % of General Administration</t>
   </si>
   <si>
     <t>Accounting - Revenue</t>
@@ -944,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:N184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1231,7 +1267,7 @@
         <v>7946</v>
       </c>
       <c r="L9" s="4">
-        <v>26946</v>
+        <v>26940</v>
       </c>
       <c r="M9" s="4">
         <v>40132</v>
@@ -1319,7 +1355,7 @@
         <v>20150</v>
       </c>
       <c r="L11" s="4">
-        <v>66877</v>
+        <v>66871</v>
       </c>
       <c r="M11" s="4">
         <v>100390</v>
@@ -1353,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -1374,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1382,43 +1418,43 @@
         <v>25</v>
       </c>
       <c r="B15" s="4">
-        <v>297.92</v>
+        <v>0</v>
       </c>
       <c r="C15" s="4">
-        <v>297.99</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>290.04</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>2085.44</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4">
-        <v>2485.93</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>2030.28</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>2030.28</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>1191.68</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4">
-        <v>1351.96</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4">
-        <v>1160.16</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4">
-        <v>19364.8</v>
+        <v>0</v>
       </c>
       <c r="M15" s="4">
-        <v>22969.35</v>
+        <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>19397.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1514,43 +1550,43 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>3728.592566666667</v>
+        <v>297.92</v>
       </c>
       <c r="C18" s="4">
-        <v>6147.77</v>
+        <v>297.99</v>
       </c>
       <c r="D18" s="4">
-        <v>5176.02</v>
+        <v>290.04</v>
       </c>
       <c r="E18" s="4">
-        <v>31525.81999722222</v>
+        <v>2085.44</v>
       </c>
       <c r="F18" s="4">
-        <v>43560.69</v>
+        <v>2485.93</v>
       </c>
       <c r="G18" s="4">
-        <v>41177.56</v>
+        <v>2030.28</v>
       </c>
       <c r="H18" s="4">
-        <v>41177.56</v>
+        <v>2030.28</v>
       </c>
       <c r="I18" s="4">
-        <v>17810.35966944444</v>
+        <v>1191.68</v>
       </c>
       <c r="J18" s="4">
-        <v>24690.58</v>
+        <v>1351.96</v>
       </c>
       <c r="K18" s="4">
-        <v>24391.66</v>
+        <v>1160.16</v>
       </c>
       <c r="L18" s="4">
-        <v>158146.5883333336</v>
+        <v>19364.8</v>
       </c>
       <c r="M18" s="4">
-        <v>191727.55</v>
+        <v>22969.35</v>
       </c>
       <c r="N18" s="4">
-        <v>220501.97</v>
+        <v>19397.91</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1646,43 +1682,43 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>1727.483333333333</v>
+        <v>3728.592566666667</v>
       </c>
       <c r="C21" s="4">
-        <v>1347.67</v>
+        <v>6147.77</v>
       </c>
       <c r="D21" s="4">
-        <v>2202.2</v>
+        <v>5176.02</v>
       </c>
       <c r="E21" s="4">
-        <v>12956.16884444444</v>
+        <v>31525.81999722222</v>
       </c>
       <c r="F21" s="4">
-        <v>14457.75</v>
+        <v>43560.69</v>
       </c>
       <c r="G21" s="4">
-        <v>14580.01</v>
+        <v>41177.56</v>
       </c>
       <c r="H21" s="4">
-        <v>14580.01</v>
+        <v>41177.56</v>
       </c>
       <c r="I21" s="4">
-        <v>7219.813130555555</v>
+        <v>17810.35966944444</v>
       </c>
       <c r="J21" s="4">
-        <v>7623.57</v>
+        <v>24690.58</v>
       </c>
       <c r="K21" s="4">
-        <v>8961.9</v>
+        <v>24391.66</v>
       </c>
       <c r="L21" s="4">
-        <v>117244.0805916666</v>
+        <v>158146.5883333334</v>
       </c>
       <c r="M21" s="4">
-        <v>133415.09</v>
+        <v>191727.55</v>
       </c>
       <c r="N21" s="4">
-        <v>137239.69</v>
+        <v>220501.97</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1778,43 +1814,43 @@
         <v>34</v>
       </c>
       <c r="B24" s="4">
-        <v>1199.529888888889</v>
+        <v>1727.483333333333</v>
       </c>
       <c r="C24" s="4">
-        <v>1698</v>
+        <v>1347.67</v>
       </c>
       <c r="D24" s="4">
-        <v>2305.83</v>
+        <v>2202.2</v>
       </c>
       <c r="E24" s="4">
-        <v>12417.57469722223</v>
+        <v>12956.16884444444</v>
       </c>
       <c r="F24" s="4">
-        <v>14406.8</v>
+        <v>14457.75</v>
       </c>
       <c r="G24" s="4">
-        <v>7855.19</v>
+        <v>14580.01</v>
       </c>
       <c r="H24" s="4">
-        <v>7855.19</v>
+        <v>14580.01</v>
       </c>
       <c r="I24" s="4">
-        <v>6171.834125</v>
+        <v>7219.813130555555</v>
       </c>
       <c r="J24" s="4">
-        <v>7422.2</v>
+        <v>7623.57</v>
       </c>
       <c r="K24" s="4">
-        <v>2451.46</v>
+        <v>8961.9</v>
       </c>
       <c r="L24" s="4">
-        <v>103699.2402166667</v>
+        <v>117244.0805916666</v>
       </c>
       <c r="M24" s="4">
-        <v>119158.6</v>
+        <v>133415.09</v>
       </c>
       <c r="N24" s="4">
-        <v>94981.5</v>
+        <v>137239.69</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1910,43 +1946,43 @@
         <v>37</v>
       </c>
       <c r="B27" s="4">
-        <v>855.3672222222224</v>
+        <v>1199.529888888889</v>
       </c>
       <c r="C27" s="4">
-        <v>808.2</v>
+        <v>1698</v>
       </c>
       <c r="D27" s="4">
-        <v>779.79</v>
+        <v>2305.83</v>
       </c>
       <c r="E27" s="4">
-        <v>4740.149722222221</v>
+        <v>12417.57469722223</v>
       </c>
       <c r="F27" s="4">
-        <v>5690.3</v>
+        <v>14406.8</v>
       </c>
       <c r="G27" s="4">
-        <v>5105.54</v>
+        <v>7855.19</v>
       </c>
       <c r="H27" s="4">
-        <v>5105.54</v>
+        <v>7855.19</v>
       </c>
       <c r="I27" s="4">
-        <v>2564.329722222222</v>
+        <v>6171.834125</v>
       </c>
       <c r="J27" s="4">
-        <v>2761.9</v>
+        <v>7422.2</v>
       </c>
       <c r="K27" s="4">
-        <v>2967.98</v>
+        <v>2451.46</v>
       </c>
       <c r="L27" s="4">
-        <v>39679.15305555555</v>
+        <v>103699.2402166667</v>
       </c>
       <c r="M27" s="4">
-        <v>39865.4</v>
+        <v>119158.6</v>
       </c>
       <c r="N27" s="4">
-        <v>41204.81</v>
+        <v>94981.5</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2042,43 +2078,43 @@
         <v>40</v>
       </c>
       <c r="B30" s="4">
-        <v>1506.225833333333</v>
+        <v>855.3672222222224</v>
       </c>
       <c r="C30" s="4">
-        <v>2303.35</v>
+        <v>808.2</v>
       </c>
       <c r="D30" s="4">
-        <v>2176.86</v>
+        <v>779.79</v>
       </c>
       <c r="E30" s="4">
-        <v>13435.76294444444</v>
+        <v>4740.149722222221</v>
       </c>
       <c r="F30" s="4">
-        <v>16444.3</v>
+        <v>5690.3</v>
       </c>
       <c r="G30" s="4">
-        <v>15131.13</v>
+        <v>5105.54</v>
       </c>
       <c r="H30" s="4">
-        <v>15131.13</v>
+        <v>5105.54</v>
       </c>
       <c r="I30" s="4">
-        <v>6448.57201388889</v>
+        <v>2564.329722222222</v>
       </c>
       <c r="J30" s="4">
-        <v>9293.6</v>
+        <v>2761.9</v>
       </c>
       <c r="K30" s="4">
-        <v>9698.92</v>
+        <v>2967.98</v>
       </c>
       <c r="L30" s="4">
-        <v>132738.0221666666</v>
+        <v>39679.15305555555</v>
       </c>
       <c r="M30" s="4">
-        <v>124704.97</v>
+        <v>39865.4</v>
       </c>
       <c r="N30" s="4">
-        <v>113085.47</v>
+        <v>41204.81</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2174,43 +2210,43 @@
         <v>43</v>
       </c>
       <c r="B33" s="4">
-        <v>1044.841577777778</v>
+        <v>1506.225833333333</v>
       </c>
       <c r="C33" s="4">
-        <v>461.23</v>
+        <v>2303.35</v>
       </c>
       <c r="D33" s="4">
-        <v>833.52</v>
+        <v>2176.86</v>
       </c>
       <c r="E33" s="4">
-        <v>6827.431147222222</v>
+        <v>13435.76294444444</v>
       </c>
       <c r="F33" s="4">
-        <v>9849.690000000001</v>
+        <v>16444.3</v>
       </c>
       <c r="G33" s="4">
-        <v>6076.06</v>
+        <v>15131.13</v>
       </c>
       <c r="H33" s="4">
-        <v>6076.06</v>
+        <v>15131.13</v>
       </c>
       <c r="I33" s="4">
-        <v>4134.289227777778</v>
+        <v>6448.57201388889</v>
       </c>
       <c r="J33" s="4">
-        <v>4265.76</v>
+        <v>9293.6</v>
       </c>
       <c r="K33" s="4">
-        <v>3825.6</v>
+        <v>9698.92</v>
       </c>
       <c r="L33" s="4">
-        <v>78018.89008611112</v>
+        <v>132738.0221666666</v>
       </c>
       <c r="M33" s="4">
-        <v>85961.67</v>
+        <v>124704.97</v>
       </c>
       <c r="N33" s="4">
-        <v>62338.33</v>
+        <v>113085.47</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2306,43 +2342,43 @@
         <v>46</v>
       </c>
       <c r="B36" s="4">
-        <v>3920.31155</v>
+        <v>1345.524911111111</v>
       </c>
       <c r="C36" s="4">
-        <v>4317.15</v>
+        <v>461.23</v>
       </c>
       <c r="D36" s="4">
-        <v>4476.95</v>
+        <v>833.52</v>
       </c>
       <c r="E36" s="4">
-        <v>29891.22364166666</v>
+        <v>7128.114480555556</v>
       </c>
       <c r="F36" s="4">
-        <v>35081.41</v>
+        <v>9849.690000000001</v>
       </c>
       <c r="G36" s="4">
-        <v>33241.94</v>
+        <v>6076.06</v>
       </c>
       <c r="H36" s="4">
-        <v>33241.94</v>
+        <v>6076.06</v>
       </c>
       <c r="I36" s="4">
-        <v>16637.5539</v>
+        <v>4434.972561111112</v>
       </c>
       <c r="J36" s="4">
-        <v>19760.8</v>
+        <v>4265.76</v>
       </c>
       <c r="K36" s="4">
-        <v>19671.63</v>
+        <v>3825.6</v>
       </c>
       <c r="L36" s="4">
-        <v>159029.9403527778</v>
+        <v>78319.57341944445</v>
       </c>
       <c r="M36" s="4">
-        <v>209789.01</v>
+        <v>85961.67</v>
       </c>
       <c r="N36" s="4">
-        <v>212860.54</v>
+        <v>62338.33</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2394,43 +2430,43 @@
         <v>48</v>
       </c>
       <c r="B38" s="4">
-        <v>104858.06</v>
+        <v>0</v>
       </c>
       <c r="C38" s="4">
-        <v>251445.26</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4">
-        <v>133707.8</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4">
-        <v>1367646.37</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4">
-        <v>2263220.28</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4">
-        <v>1610475.96</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
-        <v>1610475.96</v>
+        <v>0</v>
       </c>
       <c r="I38" s="4">
-        <v>710098.22</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4">
-        <v>1195169.4</v>
+        <v>0</v>
       </c>
       <c r="K38" s="4">
-        <v>919916.823</v>
+        <v>0</v>
       </c>
       <c r="L38" s="4">
-        <v>2412382.89</v>
+        <v>0</v>
       </c>
       <c r="M38" s="4">
-        <v>5753319.05</v>
+        <v>0</v>
       </c>
       <c r="N38" s="4">
-        <v>3197045.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2438,43 +2474,43 @@
         <v>49</v>
       </c>
       <c r="B39" s="4">
-        <v>4758.727461111112</v>
+        <v>4112.939258333333</v>
       </c>
       <c r="C39" s="4">
-        <v>1474.15</v>
+        <v>4317.15</v>
       </c>
       <c r="D39" s="4">
-        <v>1550.11</v>
+        <v>4476.95</v>
       </c>
       <c r="E39" s="4">
-        <v>33429.77341111113</v>
+        <v>30083.85135</v>
       </c>
       <c r="F39" s="4">
-        <v>9923.530000000001</v>
+        <v>35081.41</v>
       </c>
       <c r="G39" s="4">
-        <v>10743.34</v>
+        <v>33241.94</v>
       </c>
       <c r="H39" s="4">
-        <v>10743.34</v>
+        <v>33241.94</v>
       </c>
       <c r="I39" s="4">
-        <v>18983.98778888888</v>
+        <v>16830.18160833334</v>
       </c>
       <c r="J39" s="4">
-        <v>5896.6</v>
+        <v>19760.8</v>
       </c>
       <c r="K39" s="4">
-        <v>5982.44</v>
+        <v>19671.63</v>
       </c>
       <c r="L39" s="4">
-        <v>172562.4023055555</v>
+        <v>159222.5680611111</v>
       </c>
       <c r="M39" s="4">
-        <v>48032.3</v>
+        <v>209789.01</v>
       </c>
       <c r="N39" s="4">
-        <v>63607.71</v>
+        <v>212860.54</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2482,43 +2518,43 @@
         <v>50</v>
       </c>
       <c r="B40" s="5">
-        <v>4.538256249554027</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5">
-        <v>0.5862707453701851</v>
+        <v>0</v>
       </c>
       <c r="D40" s="5">
-        <v>1.159326531436461</v>
+        <v>0</v>
       </c>
       <c r="E40" s="5">
-        <v>2.444328749332412</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5">
-        <v>0.4384694714736297</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>0.6670909884305258</v>
+        <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>0.6670909884305258</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5">
-        <v>2.673431259817674</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5">
-        <v>0.4933693918201052</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>0.6503240130439488</v>
+        <v>0</v>
       </c>
       <c r="L40" s="5">
-        <v>7.153192928903398</v>
+        <v>0</v>
       </c>
       <c r="M40" s="5">
-        <v>0.8348624434447106</v>
+        <v>0</v>
       </c>
       <c r="N40" s="5">
-        <v>1.989577628522631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2526,43 +2562,43 @@
         <v>51</v>
       </c>
       <c r="B41" s="4">
-        <v>0</v>
+        <v>104858.06</v>
       </c>
       <c r="C41" s="4">
-        <v>0</v>
+        <v>251445.26</v>
       </c>
       <c r="D41" s="4">
-        <v>0</v>
+        <v>215626.25</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>1367646.37</v>
       </c>
       <c r="F41" s="4">
-        <v>0</v>
+        <v>2263220.28</v>
       </c>
       <c r="G41" s="4">
-        <v>0</v>
+        <v>2288619.49</v>
       </c>
       <c r="H41" s="4">
-        <v>0</v>
+        <v>2288619.49</v>
       </c>
       <c r="I41" s="4">
-        <v>0</v>
+        <v>710098.22</v>
       </c>
       <c r="J41" s="4">
-        <v>0</v>
+        <v>1195169.4</v>
       </c>
       <c r="K41" s="4">
-        <v>0</v>
+        <v>1262202.35</v>
       </c>
       <c r="L41" s="4">
-        <v>0</v>
+        <v>2412382.89</v>
       </c>
       <c r="M41" s="4">
-        <v>0</v>
+        <v>5753319.05</v>
       </c>
       <c r="N41" s="4">
-        <v>0</v>
+        <v>5398661.16</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2570,43 +2606,43 @@
         <v>52</v>
       </c>
       <c r="B42" s="4">
-        <v>0</v>
+        <v>5130.071905555556</v>
       </c>
       <c r="C42" s="4">
-        <v>0</v>
+        <v>1474.15</v>
       </c>
       <c r="D42" s="4">
-        <v>0</v>
+        <v>1550.11</v>
       </c>
       <c r="E42" s="4">
-        <v>0</v>
+        <v>33801.11785555557</v>
       </c>
       <c r="F42" s="4">
-        <v>0</v>
+        <v>9923.530000000001</v>
       </c>
       <c r="G42" s="4">
-        <v>276.58</v>
+        <v>10743.34</v>
       </c>
       <c r="H42" s="4">
-        <v>276.58</v>
+        <v>10743.34</v>
       </c>
       <c r="I42" s="4">
-        <v>0</v>
+        <v>19355.33223333333</v>
       </c>
       <c r="J42" s="4">
-        <v>0</v>
+        <v>5896.6</v>
       </c>
       <c r="K42" s="4">
-        <v>0</v>
+        <v>5982.44</v>
       </c>
       <c r="L42" s="4">
-        <v>0</v>
+        <v>172562.4023055553</v>
       </c>
       <c r="M42" s="4">
-        <v>0</v>
+        <v>48032.3</v>
       </c>
       <c r="N42" s="4">
-        <v>1557.58</v>
+        <v>63607.71</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2614,43 +2650,43 @@
         <v>53</v>
       </c>
       <c r="B43" s="5">
-        <v>0</v>
+        <v>4.892396355182956</v>
       </c>
       <c r="C43" s="5">
-        <v>0</v>
+        <v>0.5862707453701851</v>
       </c>
       <c r="D43" s="5">
-        <v>0</v>
+        <v>0.7188874267395551</v>
       </c>
       <c r="E43" s="5">
-        <v>0</v>
+        <v>2.471480829913333</v>
       </c>
       <c r="F43" s="5">
-        <v>0</v>
+        <v>0.4384694714736297</v>
       </c>
       <c r="G43" s="5">
-        <v>0</v>
+        <v>0.4694244738779184</v>
       </c>
       <c r="H43" s="5">
-        <v>0</v>
+        <v>0.4694244738779184</v>
       </c>
       <c r="I43" s="5">
-        <v>0</v>
+        <v>2.725726059886945</v>
       </c>
       <c r="J43" s="5">
-        <v>0</v>
+        <v>0.4933693918201052</v>
       </c>
       <c r="K43" s="5">
-        <v>0</v>
+        <v>0.4739683775743247</v>
       </c>
       <c r="L43" s="5">
-        <v>0</v>
+        <v>7.153192928903391</v>
       </c>
       <c r="M43" s="5">
-        <v>0</v>
+        <v>0.8348624434447106</v>
       </c>
       <c r="N43" s="5">
-        <v>0</v>
+        <v>1.178212673751134</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2658,43 +2694,43 @@
         <v>54</v>
       </c>
       <c r="B44" s="4">
-        <v>24280.2</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4">
-        <v>33102</v>
+        <v>0</v>
       </c>
       <c r="D44" s="4">
-        <v>28903.4</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4">
-        <v>364477.76</v>
+        <v>0</v>
       </c>
       <c r="F44" s="4">
-        <v>427140</v>
+        <v>0</v>
       </c>
       <c r="G44" s="4">
-        <v>395139.7</v>
+        <v>0</v>
       </c>
       <c r="H44" s="4">
-        <v>395139.7</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4">
-        <v>148963.56</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4">
-        <v>198234</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4">
-        <v>228706.71</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4">
-        <v>701183.63</v>
+        <v>0</v>
       </c>
       <c r="M44" s="4">
-        <v>1042417.94</v>
+        <v>0</v>
       </c>
       <c r="N44" s="4">
-        <v>821527.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2702,43 +2738,43 @@
         <v>55</v>
       </c>
       <c r="B45" s="4">
-        <v>5148.801</v>
+        <v>0</v>
       </c>
       <c r="C45" s="4">
-        <v>6750.03</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4">
-        <v>8125.15</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4">
-        <v>53800.93880555554</v>
+        <v>0</v>
       </c>
       <c r="F45" s="4">
-        <v>80943.42999999999</v>
+        <v>0</v>
       </c>
       <c r="G45" s="4">
-        <v>68423.32000000001</v>
+        <v>276.58</v>
       </c>
       <c r="H45" s="4">
-        <v>68423.32000000001</v>
+        <v>276.58</v>
       </c>
       <c r="I45" s="4">
-        <v>24661.13602777777</v>
+        <v>0</v>
       </c>
       <c r="J45" s="4">
-        <v>37905.57</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4">
-        <v>39436.15</v>
+        <v>0</v>
       </c>
       <c r="L45" s="4">
-        <v>202654.9271055552</v>
+        <v>0</v>
       </c>
       <c r="M45" s="4">
-        <v>232176.39</v>
+        <v>0</v>
       </c>
       <c r="N45" s="4">
-        <v>240433.23</v>
+        <v>1557.58</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2746,43 +2782,43 @@
         <v>56</v>
       </c>
       <c r="B46" s="5">
-        <v>21.20576024909185</v>
+        <v>0</v>
       </c>
       <c r="C46" s="5">
-        <v>20.39160775783941</v>
+        <v>0</v>
       </c>
       <c r="D46" s="5">
-        <v>28.1113986589813</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
-        <v>14.76110334017514</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5">
-        <v>18.95009364611134</v>
+        <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>17.31623524540814</v>
+        <v>0</v>
       </c>
       <c r="H46" s="5">
-        <v>17.31623524540814</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5">
-        <v>16.55514679414064</v>
+        <v>0</v>
       </c>
       <c r="J46" s="5">
-        <v>19.12162898392808</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5">
-        <v>17.24311018246907</v>
+        <v>0</v>
       </c>
       <c r="L46" s="5">
-        <v>28.90183376151483</v>
+        <v>0</v>
       </c>
       <c r="M46" s="5">
-        <v>22.27286974742588</v>
+        <v>0</v>
       </c>
       <c r="N46" s="5">
-        <v>29.26659551793157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2790,43 +2826,43 @@
         <v>57</v>
       </c>
       <c r="B47" s="4">
-        <v>600</v>
+        <v>24280.2</v>
       </c>
       <c r="C47" s="4">
-        <v>0</v>
+        <v>33102</v>
       </c>
       <c r="D47" s="4">
-        <v>1120</v>
+        <v>46244.41</v>
       </c>
       <c r="E47" s="4">
-        <v>10720</v>
+        <v>364477.76</v>
       </c>
       <c r="F47" s="4">
-        <v>0</v>
+        <v>427140</v>
       </c>
       <c r="G47" s="4">
-        <v>11440</v>
+        <v>412306.52</v>
       </c>
       <c r="H47" s="4">
-        <v>11440</v>
+        <v>412306.52</v>
       </c>
       <c r="I47" s="4">
-        <v>4800</v>
+        <v>148963.56</v>
       </c>
       <c r="J47" s="4">
-        <v>0</v>
+        <v>198234</v>
       </c>
       <c r="K47" s="4">
-        <v>6540</v>
+        <v>228427.71</v>
       </c>
       <c r="L47" s="4">
-        <v>19800</v>
+        <v>701183.63</v>
       </c>
       <c r="M47" s="4">
-        <v>0</v>
+        <v>1042417.94</v>
       </c>
       <c r="N47" s="4">
-        <v>20880</v>
+        <v>824615.8</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2834,43 +2870,43 @@
         <v>58</v>
       </c>
       <c r="B48" s="4">
-        <v>406.8595833333333</v>
+        <v>5148.800999999999</v>
       </c>
       <c r="C48" s="4">
-        <v>518.22</v>
+        <v>6750.03</v>
       </c>
       <c r="D48" s="4">
-        <v>414.77</v>
+        <v>8125.15</v>
       </c>
       <c r="E48" s="4">
-        <v>2702.532916666667</v>
+        <v>53800.93880555555</v>
       </c>
       <c r="F48" s="4">
-        <v>3590.04</v>
+        <v>80943.42999999999</v>
       </c>
       <c r="G48" s="4">
-        <v>2191.44</v>
+        <v>68423.32000000001</v>
       </c>
       <c r="H48" s="4">
-        <v>2191.44</v>
+        <v>68423.32000000001</v>
       </c>
       <c r="I48" s="4">
-        <v>1379.315</v>
+        <v>24661.13602777777</v>
       </c>
       <c r="J48" s="4">
-        <v>2072.88</v>
+        <v>37905.57</v>
       </c>
       <c r="K48" s="4">
-        <v>1227.72</v>
+        <v>39436.15</v>
       </c>
       <c r="L48" s="4">
-        <v>12387.23583333333</v>
+        <v>202654.9271055551</v>
       </c>
       <c r="M48" s="4">
-        <v>14837.82</v>
+        <v>232176.39</v>
       </c>
       <c r="N48" s="4">
-        <v>14508.6</v>
+        <v>240433.23</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2878,43 +2914,43 @@
         <v>59</v>
       </c>
       <c r="B49" s="5">
-        <v>67.80993055555555</v>
+        <v>21.20576024909185</v>
       </c>
       <c r="C49" s="5">
-        <v>0</v>
+        <v>20.39160775783941</v>
       </c>
       <c r="D49" s="5">
-        <v>37.03303571428571</v>
+        <v>17.57001548943969</v>
       </c>
       <c r="E49" s="5">
-        <v>25.2101951181592</v>
+        <v>14.76110334017514</v>
       </c>
       <c r="F49" s="5">
-        <v>0</v>
+        <v>18.95009364611134</v>
       </c>
       <c r="G49" s="5">
-        <v>19.15594405594406</v>
+        <v>16.59525539397243</v>
       </c>
       <c r="H49" s="5">
-        <v>19.15594405594406</v>
+        <v>16.59525539397243</v>
       </c>
       <c r="I49" s="5">
-        <v>28.73572916666667</v>
+        <v>16.55514679414064</v>
       </c>
       <c r="J49" s="5">
-        <v>0</v>
+        <v>19.12162898392808</v>
       </c>
       <c r="K49" s="5">
-        <v>18.77247706422018</v>
+        <v>17.26417079609125</v>
       </c>
       <c r="L49" s="5">
-        <v>62.56179713804714</v>
+        <v>28.9018337615148</v>
       </c>
       <c r="M49" s="5">
-        <v>0</v>
+        <v>22.27286974742588</v>
       </c>
       <c r="N49" s="5">
-        <v>69.48563218390805</v>
+        <v>29.1570001447947</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2922,43 +2958,43 @@
         <v>60</v>
       </c>
       <c r="B50" s="4">
-        <v>33462.68</v>
+        <v>600</v>
       </c>
       <c r="C50" s="4">
-        <v>31201.7</v>
+        <v>1130.49</v>
       </c>
       <c r="D50" s="4">
-        <v>26053.5</v>
+        <v>1120</v>
       </c>
       <c r="E50" s="4">
-        <v>338132.19</v>
+        <v>10720</v>
       </c>
       <c r="F50" s="4">
-        <v>402619</v>
+        <v>9494.549999999999</v>
       </c>
       <c r="G50" s="4">
-        <v>302488.29</v>
+        <v>11440</v>
       </c>
       <c r="H50" s="4">
-        <v>302488.29</v>
+        <v>11440</v>
       </c>
       <c r="I50" s="4">
-        <v>155916.04</v>
+        <v>4800</v>
       </c>
       <c r="J50" s="4">
-        <v>186853.9</v>
+        <v>5091.39</v>
       </c>
       <c r="K50" s="4">
-        <v>163578.33</v>
+        <v>6540</v>
       </c>
       <c r="L50" s="4">
-        <v>785729.6800000001</v>
+        <v>19800</v>
       </c>
       <c r="M50" s="4">
-        <v>1021359.4</v>
+        <v>27105.3</v>
       </c>
       <c r="N50" s="4">
-        <v>923296.6</v>
+        <v>22480</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2966,43 +3002,43 @@
         <v>61</v>
       </c>
       <c r="B51" s="4">
-        <v>0</v>
+        <v>406.8595833333333</v>
       </c>
       <c r="C51" s="4">
-        <v>2367.76</v>
+        <v>518.22</v>
       </c>
       <c r="D51" s="4">
-        <v>1215.86</v>
+        <v>414.77</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>2702.532916666667</v>
       </c>
       <c r="F51" s="4">
-        <v>16913.8</v>
+        <v>3590.04</v>
       </c>
       <c r="G51" s="4">
-        <v>12828.23</v>
+        <v>2191.44</v>
       </c>
       <c r="H51" s="4">
-        <v>12828.23</v>
+        <v>2191.44</v>
       </c>
       <c r="I51" s="4">
-        <v>0</v>
+        <v>1379.315</v>
       </c>
       <c r="J51" s="4">
-        <v>9765.040000000001</v>
+        <v>2072.88</v>
       </c>
       <c r="K51" s="4">
-        <v>7774.96</v>
+        <v>1227.72</v>
       </c>
       <c r="L51" s="4">
-        <v>7000.417127777776</v>
+        <v>12387.23583333333</v>
       </c>
       <c r="M51" s="4">
-        <v>73600.22</v>
+        <v>14837.82</v>
       </c>
       <c r="N51" s="4">
-        <v>74435.55</v>
+        <v>14508.6</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3010,43 +3046,43 @@
         <v>62</v>
       </c>
       <c r="B52" s="5">
-        <v>0</v>
+        <v>67.80993055555555</v>
       </c>
       <c r="C52" s="5">
-        <v>7.588560879695658</v>
+        <v>45.84029933922459</v>
       </c>
       <c r="D52" s="5">
-        <v>4.666781814343562</v>
+        <v>37.03303571428571</v>
       </c>
       <c r="E52" s="5">
-        <v>0</v>
+        <v>25.2101951181592</v>
       </c>
       <c r="F52" s="5">
-        <v>4.200944317083892</v>
+        <v>37.81158664707648</v>
       </c>
       <c r="G52" s="5">
-        <v>4.240901358528623</v>
+        <v>19.15594405594406</v>
       </c>
       <c r="H52" s="5">
-        <v>4.240901358528623</v>
+        <v>19.15594405594406</v>
       </c>
       <c r="I52" s="5">
-        <v>0</v>
+        <v>28.73572916666667</v>
       </c>
       <c r="J52" s="5">
-        <v>5.22602953430461</v>
+        <v>40.71343974828092</v>
       </c>
       <c r="K52" s="5">
-        <v>4.753050113667257</v>
+        <v>18.77247706422018</v>
       </c>
       <c r="L52" s="5">
-        <v>0.890944723862</v>
+        <v>62.56179713804714</v>
       </c>
       <c r="M52" s="5">
-        <v>7.206103943430686</v>
+        <v>54.74139743887727</v>
       </c>
       <c r="N52" s="5">
-        <v>8.06193264439618</v>
+        <v>64.54003558718861</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3054,43 +3090,43 @@
         <v>63</v>
       </c>
       <c r="B53" s="4">
-        <v>3312.35</v>
+        <v>33462.68</v>
       </c>
       <c r="C53" s="4">
-        <v>3561.03</v>
+        <v>31201.7</v>
       </c>
       <c r="D53" s="4">
-        <v>1174.99</v>
+        <v>26353.5</v>
       </c>
       <c r="E53" s="4">
-        <v>20449.08</v>
+        <v>338132.19</v>
       </c>
       <c r="F53" s="4">
-        <v>29907.79</v>
+        <v>402619</v>
       </c>
       <c r="G53" s="4">
-        <v>25679.09</v>
+        <v>313498.29</v>
       </c>
       <c r="H53" s="4">
-        <v>25679.09</v>
+        <v>313498.29</v>
       </c>
       <c r="I53" s="4">
-        <v>9072.040000000001</v>
+        <v>155916.04</v>
       </c>
       <c r="J53" s="4">
-        <v>16037.85</v>
+        <v>186853.9</v>
       </c>
       <c r="K53" s="4">
-        <v>15176.7</v>
+        <v>169548.33</v>
       </c>
       <c r="L53" s="4">
-        <v>59366.9</v>
+        <v>785729.6800000001</v>
       </c>
       <c r="M53" s="4">
-        <v>85381.32000000001</v>
+        <v>1021359.4</v>
       </c>
       <c r="N53" s="4">
-        <v>82679.64</v>
+        <v>943766.6</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -3101,40 +3137,40 @@
         <v>0</v>
       </c>
       <c r="C54" s="4">
-        <v>708.76</v>
+        <v>2367.76</v>
       </c>
       <c r="D54" s="4">
-        <v>126</v>
+        <v>1215.86</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
       </c>
       <c r="F54" s="4">
-        <v>4565.8</v>
+        <v>16913.8</v>
       </c>
       <c r="G54" s="4">
-        <v>126</v>
+        <v>12828.23</v>
       </c>
       <c r="H54" s="4">
-        <v>126</v>
+        <v>12828.23</v>
       </c>
       <c r="I54" s="4">
         <v>0</v>
       </c>
       <c r="J54" s="4">
-        <v>2439.52</v>
+        <v>9765.040000000001</v>
       </c>
       <c r="K54" s="4">
-        <v>0</v>
+        <v>7774.96</v>
       </c>
       <c r="L54" s="4">
-        <v>0</v>
+        <v>7000.417127777776</v>
       </c>
       <c r="M54" s="4">
-        <v>25776.22</v>
+        <v>73600.22</v>
       </c>
       <c r="N54" s="4">
-        <v>5399.28</v>
+        <v>74435.55</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3145,40 +3181,40 @@
         <v>0</v>
       </c>
       <c r="C55" s="5">
-        <v>19.90323024518187</v>
+        <v>7.588560879695658</v>
       </c>
       <c r="D55" s="5">
-        <v>10.7234955191108</v>
+        <v>4.613656630049139</v>
       </c>
       <c r="E55" s="5">
         <v>0</v>
       </c>
       <c r="F55" s="5">
-        <v>15.2662567177314</v>
+        <v>4.200944317083892</v>
       </c>
       <c r="G55" s="5">
-        <v>0.4906715931133073</v>
+        <v>4.09196171373056</v>
       </c>
       <c r="H55" s="5">
-        <v>0.4906715931133073</v>
+        <v>4.09196171373056</v>
       </c>
       <c r="I55" s="5">
         <v>0</v>
       </c>
       <c r="J55" s="5">
-        <v>15.21101643923593</v>
+        <v>5.22602953430461</v>
       </c>
       <c r="K55" s="5">
-        <v>0</v>
+        <v>4.585689519914469</v>
       </c>
       <c r="L55" s="5">
-        <v>0</v>
+        <v>0.890944723862</v>
       </c>
       <c r="M55" s="5">
-        <v>30.18953091847256</v>
+        <v>7.206103943430686</v>
       </c>
       <c r="N55" s="5">
-        <v>6.530362251214446</v>
+        <v>7.887071867133251</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3186,43 +3222,43 @@
         <v>66</v>
       </c>
       <c r="B56" s="4">
-        <v>6262.71</v>
+        <v>0</v>
       </c>
       <c r="C56" s="4">
-        <v>19494.66</v>
+        <v>0</v>
       </c>
       <c r="D56" s="4">
-        <v>10049.73</v>
+        <v>0</v>
       </c>
       <c r="E56" s="4">
-        <v>104432.01</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4">
-        <v>163728.19</v>
+        <v>0</v>
       </c>
       <c r="G56" s="4">
-        <v>112964.5</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4">
-        <v>112964.5</v>
+        <v>0</v>
       </c>
       <c r="I56" s="4">
-        <v>57086.63</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4">
-        <v>87798.16</v>
+        <v>0</v>
       </c>
       <c r="K56" s="4">
-        <v>61369.91</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4">
-        <v>312099.55</v>
+        <v>0</v>
       </c>
       <c r="M56" s="4">
-        <v>467415.53</v>
+        <v>0</v>
       </c>
       <c r="N56" s="4">
-        <v>405899.63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3230,43 +3266,43 @@
         <v>67</v>
       </c>
       <c r="B57" s="4">
-        <v>73.55500000000001</v>
+        <v>0</v>
       </c>
       <c r="C57" s="4">
-        <v>514.5</v>
+        <v>0</v>
       </c>
       <c r="D57" s="4">
-        <v>1167.39</v>
+        <v>0</v>
       </c>
       <c r="E57" s="4">
-        <v>522.8225</v>
+        <v>0</v>
       </c>
       <c r="F57" s="4">
-        <v>4947.3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="4">
-        <v>9057.77</v>
+        <v>0</v>
       </c>
       <c r="H57" s="4">
-        <v>9057.77</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4">
-        <v>174.14</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4">
-        <v>2453.52</v>
+        <v>0</v>
       </c>
       <c r="K57" s="4">
-        <v>5426.78</v>
+        <v>0</v>
       </c>
       <c r="L57" s="4">
-        <v>8935.74882222222</v>
+        <v>0</v>
       </c>
       <c r="M57" s="4">
-        <v>24400.7</v>
+        <v>0</v>
       </c>
       <c r="N57" s="4">
-        <v>50104.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3274,43 +3310,43 @@
         <v>68</v>
       </c>
       <c r="B58" s="5">
-        <v>1.174491553975835</v>
+        <v>0</v>
       </c>
       <c r="C58" s="5">
-        <v>2.639184268922874</v>
+        <v>0</v>
       </c>
       <c r="D58" s="5">
-        <v>11.61613297073653</v>
+        <v>0</v>
       </c>
       <c r="E58" s="5">
-        <v>0.500634336158042</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5">
-        <v>3.021654365079098</v>
+        <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>8.018244669785641</v>
+        <v>0</v>
       </c>
       <c r="H58" s="5">
-        <v>8.018244669785641</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5">
-        <v>0.3050451568081703</v>
+        <v>0</v>
       </c>
       <c r="J58" s="5">
-        <v>2.794500477003163</v>
+        <v>0</v>
       </c>
       <c r="K58" s="5">
-        <v>8.842737426207728</v>
+        <v>0</v>
       </c>
       <c r="L58" s="5">
-        <v>2.863108524899257</v>
+        <v>0</v>
       </c>
       <c r="M58" s="5">
-        <v>5.220344304777378</v>
+        <v>0</v>
       </c>
       <c r="N58" s="5">
-        <v>12.34416252116318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3318,43 +3354,43 @@
         <v>69</v>
       </c>
       <c r="B59" s="4">
-        <v>2844.59</v>
+        <v>3312.35</v>
       </c>
       <c r="C59" s="4">
-        <v>5122.49</v>
+        <v>4396.33</v>
       </c>
       <c r="D59" s="4">
-        <v>2452.21</v>
+        <v>1174.99</v>
       </c>
       <c r="E59" s="4">
-        <v>47683.95</v>
+        <v>20449.08</v>
       </c>
       <c r="F59" s="4">
-        <v>52411.56</v>
+        <v>36923.19</v>
       </c>
       <c r="G59" s="4">
-        <v>37412.4</v>
+        <v>36264.53</v>
       </c>
       <c r="H59" s="4">
-        <v>37412.4</v>
+        <v>36264.53</v>
       </c>
       <c r="I59" s="4">
-        <v>21937.08</v>
+        <v>9072.040000000001</v>
       </c>
       <c r="J59" s="4">
-        <v>26165</v>
+        <v>19799.81</v>
       </c>
       <c r="K59" s="4">
-        <v>24335.26</v>
+        <v>15176.7</v>
       </c>
       <c r="L59" s="4">
-        <v>127991.43</v>
+        <v>59366.9</v>
       </c>
       <c r="M59" s="4">
-        <v>153668.2</v>
+        <v>105408.95</v>
       </c>
       <c r="N59" s="4">
-        <v>142575.88</v>
+        <v>98517.89999999999</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3365,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="C60" s="4">
-        <v>921.76</v>
+        <v>708.76</v>
       </c>
       <c r="D60" s="4">
-        <v>513.3200000000001</v>
+        <v>126</v>
       </c>
       <c r="E60" s="4">
-        <v>1157.221666666667</v>
+        <v>0</v>
       </c>
       <c r="F60" s="4">
-        <v>6056.8</v>
+        <v>4565.8</v>
       </c>
       <c r="G60" s="4">
-        <v>4433.54</v>
+        <v>126</v>
       </c>
       <c r="H60" s="4">
-        <v>4433.54</v>
+        <v>126</v>
       </c>
       <c r="I60" s="4">
-        <v>682.7466666666667</v>
+        <v>0</v>
       </c>
       <c r="J60" s="4">
-        <v>3291.52</v>
+        <v>2439.52</v>
       </c>
       <c r="K60" s="4">
-        <v>2565.63</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4">
-        <v>15829.37375</v>
+        <v>0</v>
       </c>
       <c r="M60" s="4">
-        <v>28538.08</v>
+        <v>25776.22</v>
       </c>
       <c r="N60" s="4">
-        <v>36067.22</v>
+        <v>5399.28</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3409,40 +3445,40 @@
         <v>0</v>
       </c>
       <c r="C61" s="5">
-        <v>17.99437382991475</v>
+        <v>16.12162872213869</v>
       </c>
       <c r="D61" s="5">
-        <v>20.93295435545895</v>
+        <v>10.7234955191108</v>
       </c>
       <c r="E61" s="5">
-        <v>2.426857814142215</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5">
-        <v>11.55622919829137</v>
+        <v>12.36567046346754</v>
       </c>
       <c r="G61" s="5">
-        <v>11.85045599854594</v>
+        <v>0.3474469405780249</v>
       </c>
       <c r="H61" s="5">
-        <v>11.85045599854594</v>
+        <v>0.3474469405780249</v>
       </c>
       <c r="I61" s="5">
-        <v>3.112295103389634</v>
+        <v>0</v>
       </c>
       <c r="J61" s="5">
-        <v>12.57985858971909</v>
+        <v>12.32092631191915</v>
       </c>
       <c r="K61" s="5">
-        <v>10.54285016884965</v>
+        <v>0</v>
       </c>
       <c r="L61" s="5">
-        <v>12.36752628672091</v>
+        <v>0</v>
       </c>
       <c r="M61" s="5">
-        <v>18.57123334561087</v>
+        <v>24.45354023543542</v>
       </c>
       <c r="N61" s="5">
-        <v>25.29685946879654</v>
+        <v>5.480506588142865</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3450,43 +3486,43 @@
         <v>72</v>
       </c>
       <c r="B62" s="4">
-        <v>4327.03</v>
+        <v>6262.71</v>
       </c>
       <c r="C62" s="4">
-        <v>6967.15</v>
+        <v>20901.49</v>
       </c>
       <c r="D62" s="4">
-        <v>4227.01</v>
+        <v>10049.73</v>
       </c>
       <c r="E62" s="4">
-        <v>53367.22</v>
+        <v>104432.01</v>
       </c>
       <c r="F62" s="4">
-        <v>58514.46</v>
+        <v>175543.61</v>
       </c>
       <c r="G62" s="4">
-        <v>46539.17</v>
+        <v>195947.14</v>
       </c>
       <c r="H62" s="4">
-        <v>46539.17</v>
+        <v>195947.14</v>
       </c>
       <c r="I62" s="4">
-        <v>29177.19</v>
+        <v>57086.63</v>
       </c>
       <c r="J62" s="4">
-        <v>31377.99</v>
+        <v>94134.10000000001</v>
       </c>
       <c r="K62" s="4">
-        <v>26159.9</v>
+        <v>61369.91</v>
       </c>
       <c r="L62" s="4">
-        <v>124498.15</v>
+        <v>312099.55</v>
       </c>
       <c r="M62" s="4">
-        <v>167048.28</v>
+        <v>501146.4</v>
       </c>
       <c r="N62" s="4">
-        <v>119546.63</v>
+        <v>508299.42</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3494,43 +3530,43 @@
         <v>73</v>
       </c>
       <c r="B63" s="4">
-        <v>0</v>
+        <v>73.55500000000001</v>
       </c>
       <c r="C63" s="4">
-        <v>270</v>
+        <v>514.5</v>
       </c>
       <c r="D63" s="4">
-        <v>0</v>
+        <v>1167.39</v>
       </c>
       <c r="E63" s="4">
-        <v>0</v>
+        <v>522.8225</v>
       </c>
       <c r="F63" s="4">
-        <v>1890</v>
+        <v>4947.3</v>
       </c>
       <c r="G63" s="4">
-        <v>0</v>
+        <v>9057.77</v>
       </c>
       <c r="H63" s="4">
-        <v>0</v>
+        <v>9057.77</v>
       </c>
       <c r="I63" s="4">
-        <v>0</v>
+        <v>174.14</v>
       </c>
       <c r="J63" s="4">
-        <v>1080</v>
+        <v>2453.52</v>
       </c>
       <c r="K63" s="4">
-        <v>0</v>
+        <v>5426.78</v>
       </c>
       <c r="L63" s="4">
-        <v>0</v>
+        <v>8935.748822222222</v>
       </c>
       <c r="M63" s="4">
-        <v>7605</v>
+        <v>24400.7</v>
       </c>
       <c r="N63" s="4">
-        <v>0</v>
+        <v>50104.91</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3538,43 +3574,43 @@
         <v>74</v>
       </c>
       <c r="B64" s="5">
-        <v>0</v>
+        <v>1.174491553975835</v>
       </c>
       <c r="C64" s="5">
-        <v>3.875329223570614</v>
+        <v>2.461546999759347</v>
       </c>
       <c r="D64" s="5">
-        <v>0</v>
+        <v>11.61613297073653</v>
       </c>
       <c r="E64" s="5">
-        <v>0</v>
+        <v>0.500634336158042</v>
       </c>
       <c r="F64" s="5">
-        <v>3.22997084823136</v>
+        <v>2.818274045976382</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>4.622557900054066</v>
       </c>
       <c r="H64" s="5">
-        <v>0</v>
+        <v>4.622557900054066</v>
       </c>
       <c r="I64" s="5">
-        <v>0</v>
+        <v>0.3050451568081703</v>
       </c>
       <c r="J64" s="5">
-        <v>3.441903066448806</v>
+        <v>2.60640936706252</v>
       </c>
       <c r="K64" s="5">
-        <v>0</v>
+        <v>8.842737426207728</v>
       </c>
       <c r="L64" s="5">
-        <v>0</v>
+        <v>2.863108524899258</v>
       </c>
       <c r="M64" s="5">
-        <v>4.552576057652315</v>
+        <v>4.868976410885122</v>
       </c>
       <c r="N64" s="5">
-        <v>0</v>
+        <v>9.85736123798843</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3582,43 +3618,43 @@
         <v>75</v>
       </c>
       <c r="B65" s="4">
-        <v>0</v>
+        <v>2844.59</v>
       </c>
       <c r="C65" s="4">
-        <v>0</v>
+        <v>5476.29</v>
       </c>
       <c r="D65" s="4">
-        <v>0</v>
+        <v>2452.21</v>
       </c>
       <c r="E65" s="4">
-        <v>0</v>
+        <v>47683.95</v>
       </c>
       <c r="F65" s="4">
-        <v>0</v>
+        <v>55382.99</v>
       </c>
       <c r="G65" s="4">
-        <v>0</v>
+        <v>63969.84</v>
       </c>
       <c r="H65" s="4">
-        <v>0</v>
+        <v>63969.84</v>
       </c>
       <c r="I65" s="4">
-        <v>0</v>
+        <v>21937.08</v>
       </c>
       <c r="J65" s="4">
-        <v>0</v>
+        <v>27758.41</v>
       </c>
       <c r="K65" s="4">
-        <v>0</v>
+        <v>24438.96</v>
       </c>
       <c r="L65" s="4">
-        <v>0</v>
+        <v>127991.43</v>
       </c>
       <c r="M65" s="4">
-        <v>0</v>
+        <v>162462.99</v>
       </c>
       <c r="N65" s="4">
-        <v>0</v>
+        <v>184865.05</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3626,43 +3662,43 @@
         <v>76</v>
       </c>
       <c r="B66" s="4">
-        <v>1210.6</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4">
-        <v>1066.11</v>
+        <v>921.76</v>
       </c>
       <c r="D66" s="4">
-        <v>1748.34</v>
+        <v>513.3200000000001</v>
       </c>
       <c r="E66" s="4">
-        <v>9138.1</v>
+        <v>1157.221666666667</v>
       </c>
       <c r="F66" s="4">
-        <v>7462.77</v>
+        <v>6056.8</v>
       </c>
       <c r="G66" s="4">
-        <v>12451.65</v>
+        <v>4433.54</v>
       </c>
       <c r="H66" s="4">
-        <v>12451.65</v>
+        <v>4433.54</v>
       </c>
       <c r="I66" s="4">
-        <v>5105.222222222222</v>
+        <v>682.7466666666667</v>
       </c>
       <c r="J66" s="4">
-        <v>4264.44</v>
+        <v>3291.52</v>
       </c>
       <c r="K66" s="4">
-        <v>7164.57</v>
+        <v>2565.63</v>
       </c>
       <c r="L66" s="4">
-        <v>80043.39888888889</v>
+        <v>15829.37375</v>
       </c>
       <c r="M66" s="4">
-        <v>69297.14999999999</v>
+        <v>28538.08</v>
       </c>
       <c r="N66" s="4">
-        <v>108055.07</v>
+        <v>36067.22</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3673,40 +3709,40 @@
         <v>0</v>
       </c>
       <c r="C67" s="5">
-        <v>0</v>
+        <v>16.83183323016129</v>
       </c>
       <c r="D67" s="5">
-        <v>0</v>
+        <v>20.93295435545895</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>2.426857814142215</v>
       </c>
       <c r="F67" s="5">
-        <v>0</v>
+        <v>10.93620983626922</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>6.930672329335199</v>
       </c>
       <c r="H67" s="5">
-        <v>0</v>
+        <v>6.930672329335199</v>
       </c>
       <c r="I67" s="5">
-        <v>0</v>
+        <v>3.112295103389634</v>
       </c>
       <c r="J67" s="5">
-        <v>0</v>
+        <v>11.85773969042175</v>
       </c>
       <c r="K67" s="5">
-        <v>0</v>
+        <v>10.49811448605014</v>
       </c>
       <c r="L67" s="5">
-        <v>0</v>
+        <v>12.36752628672091</v>
       </c>
       <c r="M67" s="5">
-        <v>0</v>
+        <v>17.56589608500989</v>
       </c>
       <c r="N67" s="5">
-        <v>0</v>
+        <v>19.51002636788295</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3714,43 +3750,43 @@
         <v>78</v>
       </c>
       <c r="B68" s="4">
-        <v>4865.39</v>
+        <v>4327.03</v>
       </c>
       <c r="C68" s="4">
-        <v>8302.059999999999</v>
+        <v>7503.08</v>
       </c>
       <c r="D68" s="4">
-        <v>6252.4</v>
+        <v>4227.01</v>
       </c>
       <c r="E68" s="4">
-        <v>55025.89</v>
+        <v>53367.22</v>
       </c>
       <c r="F68" s="4">
-        <v>69725.86</v>
+        <v>63015.55</v>
       </c>
       <c r="G68" s="4">
-        <v>60674.53</v>
+        <v>65747.09</v>
       </c>
       <c r="H68" s="4">
-        <v>60674.53</v>
+        <v>65747.09</v>
       </c>
       <c r="I68" s="4">
-        <v>28832.25</v>
+        <v>29177.19</v>
       </c>
       <c r="J68" s="4">
-        <v>37390.04</v>
+        <v>33791.67</v>
       </c>
       <c r="K68" s="4">
-        <v>33101.29</v>
+        <v>26159.9</v>
       </c>
       <c r="L68" s="4">
-        <v>149692.08</v>
+        <v>124498.15</v>
       </c>
       <c r="M68" s="4">
-        <v>199055.11</v>
+        <v>179898.02</v>
       </c>
       <c r="N68" s="4">
-        <v>175622.71</v>
+        <v>140146.82</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3758,43 +3794,43 @@
         <v>79</v>
       </c>
       <c r="B69" s="4">
-        <v>390.4451388888889</v>
+        <v>0</v>
       </c>
       <c r="C69" s="4">
-        <v>970.5</v>
+        <v>270</v>
       </c>
       <c r="D69" s="4">
-        <v>858.74</v>
+        <v>0</v>
       </c>
       <c r="E69" s="4">
-        <v>5973.275094444447</v>
+        <v>0</v>
       </c>
       <c r="F69" s="4">
-        <v>6900.74</v>
+        <v>1890</v>
       </c>
       <c r="G69" s="4">
-        <v>7737.85</v>
+        <v>0</v>
       </c>
       <c r="H69" s="4">
-        <v>7737.85</v>
+        <v>0</v>
       </c>
       <c r="I69" s="4">
-        <v>3330.092555555556</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4">
-        <v>3819.24</v>
+        <v>1080</v>
       </c>
       <c r="K69" s="4">
-        <v>4462.17</v>
+        <v>0</v>
       </c>
       <c r="L69" s="4">
-        <v>28386.83248611111</v>
+        <v>0</v>
       </c>
       <c r="M69" s="4">
-        <v>37075.58</v>
+        <v>7605</v>
       </c>
       <c r="N69" s="4">
-        <v>36039.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3802,43 +3838,43 @@
         <v>80</v>
       </c>
       <c r="B70" s="5">
-        <v>8.024950495004282</v>
+        <v>0</v>
       </c>
       <c r="C70" s="5">
-        <v>11.68986974317218</v>
+        <v>3.598522206880375</v>
       </c>
       <c r="D70" s="5">
-        <v>13.73456592668415</v>
+        <v>0</v>
       </c>
       <c r="E70" s="5">
-        <v>10.85539024347348</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5">
-        <v>9.896959320401354</v>
+        <v>2.999259706532752</v>
       </c>
       <c r="G70" s="5">
-        <v>12.75304481138956</v>
+        <v>0</v>
       </c>
       <c r="H70" s="5">
-        <v>12.75304481138956</v>
+        <v>0</v>
       </c>
       <c r="I70" s="5">
-        <v>11.54988790522958</v>
+        <v>0</v>
       </c>
       <c r="J70" s="5">
-        <v>10.21459190736356</v>
+        <v>3.196053938736973</v>
       </c>
       <c r="K70" s="5">
-        <v>13.48035076578586</v>
+        <v>0</v>
       </c>
       <c r="L70" s="5">
-        <v>18.96348322911347</v>
+        <v>0</v>
       </c>
       <c r="M70" s="5">
-        <v>18.62578659749051</v>
+        <v>4.227395054153459</v>
       </c>
       <c r="N70" s="5">
-        <v>20.52070600664344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3846,43 +3882,43 @@
         <v>81</v>
       </c>
       <c r="B71" s="4">
-        <v>2858.73</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4">
-        <v>12073</v>
+        <v>0</v>
       </c>
       <c r="D71" s="4">
-        <v>12132.99</v>
+        <v>0</v>
       </c>
       <c r="E71" s="4">
-        <v>32011.97</v>
+        <v>0</v>
       </c>
       <c r="F71" s="4">
-        <v>101396.48</v>
+        <v>0</v>
       </c>
       <c r="G71" s="4">
-        <v>95563.3</v>
+        <v>0</v>
       </c>
       <c r="H71" s="4">
-        <v>95563.3</v>
+        <v>0</v>
       </c>
       <c r="I71" s="4">
-        <v>21916.52</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4">
-        <v>54373.2</v>
+        <v>0</v>
       </c>
       <c r="K71" s="4">
-        <v>52144.78</v>
+        <v>0</v>
       </c>
       <c r="L71" s="4">
-        <v>37855.29</v>
+        <v>0</v>
       </c>
       <c r="M71" s="4">
-        <v>221388.31</v>
+        <v>0</v>
       </c>
       <c r="N71" s="4">
-        <v>193775.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3890,43 +3926,43 @@
         <v>82</v>
       </c>
       <c r="B72" s="4">
-        <v>1308.221105555556</v>
+        <v>1210.6</v>
       </c>
       <c r="C72" s="4">
-        <v>2979.22</v>
+        <v>1066.11</v>
       </c>
       <c r="D72" s="4">
-        <v>2424.34</v>
+        <v>1748.34</v>
       </c>
       <c r="E72" s="4">
-        <v>11636.92555000001</v>
+        <v>9138.1</v>
       </c>
       <c r="F72" s="4">
-        <v>17618.93</v>
+        <v>7462.77</v>
       </c>
       <c r="G72" s="4">
-        <v>20320.64</v>
+        <v>12451.65</v>
       </c>
       <c r="H72" s="4">
-        <v>20320.64</v>
+        <v>12451.65</v>
       </c>
       <c r="I72" s="4">
-        <v>6300.746766666666</v>
+        <v>5105.222222222222</v>
       </c>
       <c r="J72" s="4">
-        <v>10960.02</v>
+        <v>4264.44</v>
       </c>
       <c r="K72" s="4">
-        <v>12377.67</v>
+        <v>7164.57</v>
       </c>
       <c r="L72" s="4">
-        <v>25442.39589444442</v>
+        <v>80043.39888888889</v>
       </c>
       <c r="M72" s="4">
-        <v>55235.56</v>
+        <v>69297.14999999999</v>
       </c>
       <c r="N72" s="4">
-        <v>54986.67</v>
+        <v>108055.07</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3934,43 +3970,43 @@
         <v>83</v>
       </c>
       <c r="B73" s="5">
-        <v>45.76231772694713</v>
+        <v>0</v>
       </c>
       <c r="C73" s="5">
-        <v>24.67671664043734</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5">
-        <v>19.98138958327667</v>
+        <v>0</v>
       </c>
       <c r="E73" s="5">
-        <v>36.35179450061963</v>
+        <v>0</v>
       </c>
       <c r="F73" s="5">
-        <v>17.37627381147748</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>21.26406266840931</v>
+        <v>0</v>
       </c>
       <c r="H73" s="5">
-        <v>21.26406266840931</v>
+        <v>0</v>
       </c>
       <c r="I73" s="5">
-        <v>28.74884683638948</v>
+        <v>0</v>
       </c>
       <c r="J73" s="5">
-        <v>20.15702588775353</v>
+        <v>0</v>
       </c>
       <c r="K73" s="5">
-        <v>23.73712191325766</v>
+        <v>0</v>
       </c>
       <c r="L73" s="5">
-        <v>67.20961824475368</v>
+        <v>0</v>
       </c>
       <c r="M73" s="5">
-        <v>24.94962809915302</v>
+        <v>0</v>
       </c>
       <c r="N73" s="5">
-        <v>28.37655381878189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3978,43 +4014,43 @@
         <v>84</v>
       </c>
       <c r="B74" s="4">
-        <v>0</v>
+        <v>4865.39</v>
       </c>
       <c r="C74" s="4">
-        <v>0</v>
+        <v>8302.059999999999</v>
       </c>
       <c r="D74" s="4">
-        <v>0</v>
+        <v>6252.4</v>
       </c>
       <c r="E74" s="4">
-        <v>0</v>
+        <v>55025.89</v>
       </c>
       <c r="F74" s="4">
-        <v>0</v>
+        <v>69725.86</v>
       </c>
       <c r="G74" s="4">
-        <v>0</v>
+        <v>76600.64999999999</v>
       </c>
       <c r="H74" s="4">
-        <v>0</v>
+        <v>76600.64999999999</v>
       </c>
       <c r="I74" s="4">
-        <v>0</v>
+        <v>28832.25</v>
       </c>
       <c r="J74" s="4">
-        <v>0</v>
+        <v>37390.04</v>
       </c>
       <c r="K74" s="4">
-        <v>0</v>
+        <v>33101.29</v>
       </c>
       <c r="L74" s="4">
-        <v>0</v>
+        <v>149692.08</v>
       </c>
       <c r="M74" s="4">
-        <v>0</v>
+        <v>199055.11</v>
       </c>
       <c r="N74" s="4">
-        <v>0</v>
+        <v>196986.67</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4022,43 +4058,43 @@
         <v>85</v>
       </c>
       <c r="B75" s="4">
-        <v>0</v>
+        <v>390.4451388888889</v>
       </c>
       <c r="C75" s="4">
-        <v>0</v>
+        <v>970.5</v>
       </c>
       <c r="D75" s="4">
-        <v>0</v>
+        <v>858.74</v>
       </c>
       <c r="E75" s="4">
-        <v>0</v>
+        <v>5973.275094444447</v>
       </c>
       <c r="F75" s="4">
-        <v>0</v>
+        <v>6900.74</v>
       </c>
       <c r="G75" s="4">
-        <v>0</v>
+        <v>7737.85</v>
       </c>
       <c r="H75" s="4">
-        <v>0</v>
+        <v>7737.85</v>
       </c>
       <c r="I75" s="4">
-        <v>0</v>
+        <v>3330.092555555555</v>
       </c>
       <c r="J75" s="4">
-        <v>0</v>
+        <v>3819.24</v>
       </c>
       <c r="K75" s="4">
-        <v>0</v>
+        <v>4462.17</v>
       </c>
       <c r="L75" s="4">
-        <v>0</v>
+        <v>28386.83248611112</v>
       </c>
       <c r="M75" s="4">
-        <v>0</v>
+        <v>37075.58</v>
       </c>
       <c r="N75" s="4">
-        <v>1777.14</v>
+        <v>36039.02</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4066,43 +4102,43 @@
         <v>86</v>
       </c>
       <c r="B76" s="5">
-        <v>0</v>
+        <v>8.024950495004282</v>
       </c>
       <c r="C76" s="5">
-        <v>0</v>
+        <v>11.68986974317218</v>
       </c>
       <c r="D76" s="5">
-        <v>0</v>
+        <v>13.73456592668415</v>
       </c>
       <c r="E76" s="5">
-        <v>0</v>
+        <v>10.85539024347348</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>9.896959320401354</v>
       </c>
       <c r="G76" s="5">
-        <v>0</v>
+        <v>10.10154613570512</v>
       </c>
       <c r="H76" s="5">
-        <v>0</v>
+        <v>10.10154613570512</v>
       </c>
       <c r="I76" s="5">
-        <v>0</v>
+        <v>11.54988790522958</v>
       </c>
       <c r="J76" s="5">
-        <v>0</v>
+        <v>10.21459190736356</v>
       </c>
       <c r="K76" s="5">
-        <v>0</v>
+        <v>13.48035076578586</v>
       </c>
       <c r="L76" s="5">
-        <v>0</v>
+        <v>18.96348322911347</v>
       </c>
       <c r="M76" s="5">
-        <v>0</v>
+        <v>18.62578659749051</v>
       </c>
       <c r="N76" s="5">
-        <v>0</v>
+        <v>18.29515672304121</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -4110,43 +4146,43 @@
         <v>87</v>
       </c>
       <c r="B77" s="4">
-        <v>1391.75</v>
+        <v>2858.73</v>
       </c>
       <c r="C77" s="4">
-        <v>1773.47</v>
+        <v>12073</v>
       </c>
       <c r="D77" s="4">
-        <v>1594.6</v>
+        <v>12132.99</v>
       </c>
       <c r="E77" s="4">
-        <v>13607.03</v>
+        <v>32011.97</v>
       </c>
       <c r="F77" s="4">
-        <v>14894.69</v>
+        <v>101396.48</v>
       </c>
       <c r="G77" s="4">
-        <v>13385.81</v>
+        <v>145200.78</v>
       </c>
       <c r="H77" s="4">
-        <v>13385.81</v>
+        <v>145200.78</v>
       </c>
       <c r="I77" s="4">
-        <v>6624.13</v>
+        <v>21916.52</v>
       </c>
       <c r="J77" s="4">
-        <v>7987.17</v>
+        <v>54373.2</v>
       </c>
       <c r="K77" s="4">
-        <v>7389.2</v>
+        <v>52086.36</v>
       </c>
       <c r="L77" s="4">
-        <v>23958.09</v>
+        <v>37855.29</v>
       </c>
       <c r="M77" s="4">
-        <v>36572.14</v>
+        <v>221388.31</v>
       </c>
       <c r="N77" s="4">
-        <v>23668.8</v>
+        <v>207902</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4154,43 +4190,43 @@
         <v>88</v>
       </c>
       <c r="B78" s="4">
-        <v>306.6573222222222</v>
+        <v>1488.97555</v>
       </c>
       <c r="C78" s="4">
-        <v>244.43</v>
+        <v>2979.22</v>
       </c>
       <c r="D78" s="4">
-        <v>259.2</v>
+        <v>2424.34</v>
       </c>
       <c r="E78" s="4">
-        <v>2418.881944444445</v>
+        <v>11817.67999444445</v>
       </c>
       <c r="F78" s="4">
-        <v>1681.41</v>
+        <v>17618.93</v>
       </c>
       <c r="G78" s="4">
-        <v>1027.75</v>
+        <v>20320.64</v>
       </c>
       <c r="H78" s="4">
-        <v>1027.75</v>
+        <v>20320.64</v>
       </c>
       <c r="I78" s="4">
-        <v>1224.848077777778</v>
+        <v>6481.501211111111</v>
       </c>
       <c r="J78" s="4">
-        <v>962.92</v>
+        <v>10960.02</v>
       </c>
       <c r="K78" s="4">
-        <v>647.5</v>
+        <v>12377.67</v>
       </c>
       <c r="L78" s="4">
-        <v>4910.986655555555</v>
+        <v>25623.15033888887</v>
       </c>
       <c r="M78" s="4">
-        <v>9388.15</v>
+        <v>55235.56</v>
       </c>
       <c r="N78" s="4">
-        <v>4245.55</v>
+        <v>54986.67</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4198,43 +4234,43 @@
         <v>89</v>
       </c>
       <c r="B79" s="5">
-        <v>22.03393728918428</v>
+        <v>52.08521091533652</v>
       </c>
       <c r="C79" s="5">
-        <v>13.78258442488455</v>
+        <v>24.67671664043734</v>
       </c>
       <c r="D79" s="5">
-        <v>16.25486015301643</v>
+        <v>19.98138958327667</v>
       </c>
       <c r="E79" s="5">
-        <v>17.77670766099909</v>
+        <v>36.91644092645486</v>
       </c>
       <c r="F79" s="5">
-        <v>11.28865387597862</v>
+        <v>17.37627381147748</v>
       </c>
       <c r="G79" s="5">
-        <v>7.677906678788957</v>
+        <v>13.99485595049834</v>
       </c>
       <c r="H79" s="5">
-        <v>7.677906678788957</v>
+        <v>13.99485595049834</v>
       </c>
       <c r="I79" s="5">
-        <v>18.49070108493912</v>
+        <v>29.5735874632976</v>
       </c>
       <c r="J79" s="5">
-        <v>12.05583454465098</v>
+        <v>20.15702588775353</v>
       </c>
       <c r="K79" s="5">
-        <v>8.762788935202728</v>
+        <v>23.76374544122492</v>
       </c>
       <c r="L79" s="5">
-        <v>20.49823944878559</v>
+        <v>67.68710618486575</v>
       </c>
       <c r="M79" s="5">
-        <v>25.67022329018755</v>
+        <v>24.94962809915302</v>
       </c>
       <c r="N79" s="5">
-        <v>17.93732677617792</v>
+        <v>26.44836028513434</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -4242,43 +4278,43 @@
         <v>90</v>
       </c>
       <c r="B80" s="4">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="C80" s="4">
-        <v>1439.88</v>
+        <v>0</v>
       </c>
       <c r="D80" s="4">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="E80" s="4">
-        <v>11567.26</v>
+        <v>0</v>
       </c>
       <c r="F80" s="4">
-        <v>18891.39</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4">
-        <v>5870</v>
+        <v>0</v>
       </c>
       <c r="H80" s="4">
-        <v>5870</v>
+        <v>0</v>
       </c>
       <c r="I80" s="4">
-        <v>3065</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4">
-        <v>9842.5</v>
+        <v>0</v>
       </c>
       <c r="K80" s="4">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="L80" s="4">
-        <v>18661.09</v>
+        <v>0</v>
       </c>
       <c r="M80" s="4">
-        <v>56235.58</v>
+        <v>0</v>
       </c>
       <c r="N80" s="4">
-        <v>11878.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4286,43 +4322,43 @@
         <v>91</v>
       </c>
       <c r="B81" s="4">
-        <v>573.2480555555554</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4">
-        <v>553.9</v>
+        <v>0</v>
       </c>
       <c r="D81" s="4">
-        <v>573.55</v>
+        <v>0</v>
       </c>
       <c r="E81" s="4">
-        <v>6260.320133333332</v>
+        <v>0</v>
       </c>
       <c r="F81" s="4">
-        <v>3781.3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4">
-        <v>4154.68</v>
+        <v>0</v>
       </c>
       <c r="H81" s="4">
-        <v>4154.68</v>
+        <v>0</v>
       </c>
       <c r="I81" s="4">
-        <v>3106.161833333333</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4">
-        <v>2247.6</v>
+        <v>0</v>
       </c>
       <c r="K81" s="4">
-        <v>2447.41</v>
+        <v>0</v>
       </c>
       <c r="L81" s="4">
-        <v>38140.24713888889</v>
+        <v>0</v>
       </c>
       <c r="M81" s="4">
-        <v>26391.42</v>
+        <v>0</v>
       </c>
       <c r="N81" s="4">
-        <v>22525.69</v>
+        <v>1777.14</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4330,43 +4366,43 @@
         <v>92</v>
       </c>
       <c r="B82" s="5">
-        <v>140.5019744008714</v>
+        <v>0</v>
       </c>
       <c r="C82" s="5">
-        <v>38.46848348473483</v>
+        <v>0</v>
       </c>
       <c r="D82" s="5">
-        <v>185.016129032258</v>
+        <v>0</v>
       </c>
       <c r="E82" s="5">
-        <v>54.12102895009995</v>
+        <v>0</v>
       </c>
       <c r="F82" s="5">
-        <v>20.01599670537743</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>70.77819420783646</v>
+        <v>0</v>
       </c>
       <c r="H82" s="5">
-        <v>70.77819420783646</v>
+        <v>0</v>
       </c>
       <c r="I82" s="5">
-        <v>101.342963567156</v>
+        <v>0</v>
       </c>
       <c r="J82" s="5">
-        <v>22.83566167132334</v>
+        <v>0</v>
       </c>
       <c r="K82" s="5">
-        <v>69.926</v>
+        <v>0</v>
       </c>
       <c r="L82" s="5">
-        <v>204.3838121936548</v>
+        <v>0</v>
       </c>
       <c r="M82" s="5">
-        <v>46.93011079462504</v>
+        <v>0</v>
       </c>
       <c r="N82" s="5">
-        <v>189.6408342088957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4374,43 +4410,43 @@
         <v>93</v>
       </c>
       <c r="B83" s="4">
-        <v>4781.68</v>
+        <v>1391.75</v>
       </c>
       <c r="C83" s="4">
-        <v>7742.43</v>
+        <v>1773.47</v>
       </c>
       <c r="D83" s="4">
-        <v>6377.63</v>
+        <v>1594.6</v>
       </c>
       <c r="E83" s="4">
-        <v>54627.45</v>
+        <v>13607.03</v>
       </c>
       <c r="F83" s="4">
-        <v>65025.65</v>
+        <v>14894.69</v>
       </c>
       <c r="G83" s="4">
-        <v>50924.33</v>
+        <v>13627.15</v>
       </c>
       <c r="H83" s="4">
-        <v>50924.33</v>
+        <v>13627.15</v>
       </c>
       <c r="I83" s="4">
-        <v>26956.17</v>
+        <v>6624.13</v>
       </c>
       <c r="J83" s="4">
-        <v>34869.58</v>
+        <v>7987.17</v>
       </c>
       <c r="K83" s="4">
-        <v>29096.36</v>
+        <v>7389.2</v>
       </c>
       <c r="L83" s="4">
-        <v>112910.12</v>
+        <v>23958.09</v>
       </c>
       <c r="M83" s="4">
-        <v>160365.93</v>
+        <v>36572.14</v>
       </c>
       <c r="N83" s="4">
-        <v>102670.27</v>
+        <v>24187.9</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4418,43 +4454,43 @@
         <v>94</v>
       </c>
       <c r="B84" s="4">
-        <v>1757.860605555556</v>
+        <v>306.6573222222222</v>
       </c>
       <c r="C84" s="4">
-        <v>1492.73</v>
+        <v>244.43</v>
       </c>
       <c r="D84" s="4">
-        <v>2053.32</v>
+        <v>259.2</v>
       </c>
       <c r="E84" s="4">
-        <v>13904.34706111112</v>
+        <v>2418.881944444444</v>
       </c>
       <c r="F84" s="4">
-        <v>11077.11</v>
+        <v>1681.41</v>
       </c>
       <c r="G84" s="4">
-        <v>15502.48</v>
+        <v>1027.75</v>
       </c>
       <c r="H84" s="4">
-        <v>15502.48</v>
+        <v>1027.75</v>
       </c>
       <c r="I84" s="4">
-        <v>7065.166022222223</v>
+        <v>1224.848077777778</v>
       </c>
       <c r="J84" s="4">
-        <v>5990.92</v>
+        <v>962.92</v>
       </c>
       <c r="K84" s="4">
-        <v>9062.190000000001</v>
+        <v>647.5</v>
       </c>
       <c r="L84" s="4">
-        <v>50679.6176277778</v>
+        <v>4910.986655555555</v>
       </c>
       <c r="M84" s="4">
-        <v>49257.45</v>
+        <v>9388.15</v>
       </c>
       <c r="N84" s="4">
-        <v>45800.68</v>
+        <v>4245.55</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4462,43 +4498,43 @@
         <v>95</v>
       </c>
       <c r="B85" s="5">
-        <v>36.76240579786928</v>
+        <v>22.03393728918428</v>
       </c>
       <c r="C85" s="5">
-        <v>19.27986433199913</v>
+        <v>13.78258442488455</v>
       </c>
       <c r="D85" s="5">
-        <v>32.19565888896032</v>
+        <v>16.25486015301643</v>
       </c>
       <c r="E85" s="5">
-        <v>25.45304066199525</v>
+        <v>17.77670766099909</v>
       </c>
       <c r="F85" s="5">
-        <v>17.0349854249823</v>
+        <v>11.28865387597862</v>
       </c>
       <c r="G85" s="5">
-        <v>30.44218745735093</v>
+        <v>7.541929163471453</v>
       </c>
       <c r="H85" s="5">
-        <v>30.44218745735093</v>
+        <v>7.541929163471453</v>
       </c>
       <c r="I85" s="5">
-        <v>26.20982885262343</v>
+        <v>18.49070108493912</v>
       </c>
       <c r="J85" s="5">
-        <v>17.18093535970321</v>
+        <v>12.05583454465098</v>
       </c>
       <c r="K85" s="5">
-        <v>31.14544224775883</v>
+        <v>8.762788935202728</v>
       </c>
       <c r="L85" s="5">
-        <v>44.88492052597039</v>
+        <v>20.49823944878559</v>
       </c>
       <c r="M85" s="5">
-        <v>30.7156576212915</v>
+        <v>25.67022329018755</v>
       </c>
       <c r="N85" s="5">
-        <v>44.60948627095263</v>
+        <v>17.55237122693578</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4506,43 +4542,43 @@
         <v>96</v>
       </c>
       <c r="B86" s="4">
-        <v>11858.95</v>
+        <v>408</v>
       </c>
       <c r="C86" s="4">
-        <v>23110.93</v>
+        <v>1439.88</v>
       </c>
       <c r="D86" s="4">
-        <v>14276.03</v>
+        <v>310</v>
       </c>
       <c r="E86" s="4">
-        <v>151264.33</v>
+        <v>11567.26</v>
       </c>
       <c r="F86" s="4">
-        <v>242510.64</v>
+        <v>18891.39</v>
       </c>
       <c r="G86" s="4">
-        <v>152857.3</v>
+        <v>5871.44</v>
       </c>
       <c r="H86" s="4">
-        <v>152857.3</v>
+        <v>5871.44</v>
       </c>
       <c r="I86" s="4">
-        <v>69990.73</v>
+        <v>3065</v>
       </c>
       <c r="J86" s="4">
-        <v>104084.68</v>
+        <v>9842.5</v>
       </c>
       <c r="K86" s="4">
-        <v>80495.28999999999</v>
+        <v>3501.44</v>
       </c>
       <c r="L86" s="4">
-        <v>391967.57</v>
+        <v>18661.09</v>
       </c>
       <c r="M86" s="4">
-        <v>617864.85</v>
+        <v>56235.58</v>
       </c>
       <c r="N86" s="4">
-        <v>482412.3</v>
+        <v>47191.04</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4550,43 +4586,43 @@
         <v>97</v>
       </c>
       <c r="B87" s="4">
-        <v>2356.6277</v>
+        <v>573.2480555555555</v>
       </c>
       <c r="C87" s="4">
-        <v>3770.7</v>
+        <v>553.9</v>
       </c>
       <c r="D87" s="4">
-        <v>2349.82</v>
+        <v>573.55</v>
       </c>
       <c r="E87" s="4">
-        <v>19843.56455833334</v>
+        <v>6260.320133333333</v>
       </c>
       <c r="F87" s="4">
-        <v>26319.7</v>
+        <v>3781.3</v>
       </c>
       <c r="G87" s="4">
-        <v>23127.37</v>
+        <v>4154.68</v>
       </c>
       <c r="H87" s="4">
-        <v>23127.37</v>
+        <v>4154.68</v>
       </c>
       <c r="I87" s="4">
-        <v>10831.56358055556</v>
+        <v>3106.161833333333</v>
       </c>
       <c r="J87" s="4">
-        <v>15052</v>
+        <v>2247.6</v>
       </c>
       <c r="K87" s="4">
-        <v>13806.57</v>
+        <v>2447.41</v>
       </c>
       <c r="L87" s="4">
-        <v>97845.70983055564</v>
+        <v>38140.24713888888</v>
       </c>
       <c r="M87" s="4">
-        <v>121533.42</v>
+        <v>26391.42</v>
       </c>
       <c r="N87" s="4">
-        <v>105979.34</v>
+        <v>22525.69</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4594,43 +4630,43 @@
         <v>98</v>
       </c>
       <c r="B88" s="5">
-        <v>19.87214466710796</v>
+        <v>140.5019744008715</v>
       </c>
       <c r="C88" s="5">
-        <v>16.31565670442513</v>
+        <v>38.46848348473483</v>
       </c>
       <c r="D88" s="5">
-        <v>16.45989816496603</v>
+        <v>185.016129032258</v>
       </c>
       <c r="E88" s="5">
-        <v>13.11846921103828</v>
+        <v>54.12102895009996</v>
       </c>
       <c r="F88" s="5">
-        <v>10.85300834635544</v>
+        <v>20.01599670537743</v>
       </c>
       <c r="G88" s="5">
-        <v>15.13003958594061</v>
+        <v>70.76083550202337</v>
       </c>
       <c r="H88" s="5">
-        <v>15.13003958594061</v>
+        <v>70.76083550202337</v>
       </c>
       <c r="I88" s="5">
-        <v>15.4757116843267</v>
+        <v>101.342963567156</v>
       </c>
       <c r="J88" s="5">
-        <v>14.4613020859554</v>
+        <v>22.83566167132334</v>
       </c>
       <c r="K88" s="5">
-        <v>17.15202218663974</v>
+        <v>69.89724227746298</v>
       </c>
       <c r="L88" s="5">
-        <v>24.96270541732716</v>
+        <v>204.3838121936547</v>
       </c>
       <c r="M88" s="5">
-        <v>19.66990353958475</v>
+        <v>46.93011079462504</v>
       </c>
       <c r="N88" s="5">
-        <v>21.96862310517373</v>
+        <v>47.73298066751654</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4638,43 +4674,43 @@
         <v>99</v>
       </c>
       <c r="B89" s="4">
-        <v>2225.97</v>
+        <v>4781.68</v>
       </c>
       <c r="C89" s="4">
-        <v>3938.41</v>
+        <v>7742.43</v>
       </c>
       <c r="D89" s="4">
-        <v>2794.51</v>
+        <v>6377.63</v>
       </c>
       <c r="E89" s="4">
-        <v>37855.59</v>
+        <v>54627.45</v>
       </c>
       <c r="F89" s="4">
-        <v>33077.08</v>
+        <v>65025.65</v>
       </c>
       <c r="G89" s="4">
-        <v>36088.16</v>
+        <v>62368.44</v>
       </c>
       <c r="H89" s="4">
-        <v>36088.16</v>
+        <v>62368.44</v>
       </c>
       <c r="I89" s="4">
-        <v>17077.99</v>
+        <v>26956.17</v>
       </c>
       <c r="J89" s="4">
-        <v>17737.37</v>
+        <v>34869.58</v>
       </c>
       <c r="K89" s="4">
-        <v>19680.77</v>
+        <v>29096.36</v>
       </c>
       <c r="L89" s="4">
-        <v>101728.76</v>
+        <v>112910.12</v>
       </c>
       <c r="M89" s="4">
-        <v>98883.98</v>
+        <v>160365.93</v>
       </c>
       <c r="N89" s="4">
-        <v>79208.35000000001</v>
+        <v>116660.01</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4682,43 +4718,43 @@
         <v>100</v>
       </c>
       <c r="B90" s="4">
-        <v>262.0532333333333</v>
+        <v>1757.860605555556</v>
       </c>
       <c r="C90" s="4">
-        <v>404.55</v>
+        <v>1492.73</v>
       </c>
       <c r="D90" s="4">
-        <v>483.14</v>
+        <v>2053.32</v>
       </c>
       <c r="E90" s="4">
-        <v>1976.845822222222</v>
+        <v>13904.34706111112</v>
       </c>
       <c r="F90" s="4">
-        <v>2883.65</v>
+        <v>11077.11</v>
       </c>
       <c r="G90" s="4">
-        <v>2805.62</v>
+        <v>15502.48</v>
       </c>
       <c r="H90" s="4">
-        <v>2805.62</v>
+        <v>15502.48</v>
       </c>
       <c r="I90" s="4">
-        <v>1015.387322222222</v>
+        <v>7065.166022222224</v>
       </c>
       <c r="J90" s="4">
-        <v>1644.1</v>
+        <v>5990.92</v>
       </c>
       <c r="K90" s="4">
-        <v>1518.14</v>
+        <v>9062.190000000001</v>
       </c>
       <c r="L90" s="4">
-        <v>11296.55876111111</v>
+        <v>50679.61762777781</v>
       </c>
       <c r="M90" s="4">
-        <v>18146</v>
+        <v>49257.45</v>
       </c>
       <c r="N90" s="4">
-        <v>13640.17</v>
+        <v>45800.68</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4726,43 +4762,43 @@
         <v>101</v>
       </c>
       <c r="B91" s="5">
-        <v>11.77254110941896</v>
+        <v>36.76240579786928</v>
       </c>
       <c r="C91" s="5">
-        <v>10.27191176134532</v>
+        <v>19.27986433199913</v>
       </c>
       <c r="D91" s="5">
-        <v>17.28889859045056</v>
+        <v>32.19565888896032</v>
       </c>
       <c r="E91" s="5">
-        <v>5.222071092333318</v>
+        <v>25.45304066199525</v>
       </c>
       <c r="F91" s="5">
-        <v>8.717970268234076</v>
+        <v>17.0349854249823</v>
       </c>
       <c r="G91" s="5">
-        <v>7.774350368652764</v>
+        <v>24.85628949513568</v>
       </c>
       <c r="H91" s="5">
-        <v>7.774350368652764</v>
+        <v>24.85628949513568</v>
       </c>
       <c r="I91" s="5">
-        <v>5.945590331310781</v>
+        <v>26.20982885262344</v>
       </c>
       <c r="J91" s="5">
-        <v>9.269130654657371</v>
+        <v>17.18093535970321</v>
       </c>
       <c r="K91" s="5">
-        <v>7.713824205048889</v>
+        <v>31.14544224775883</v>
       </c>
       <c r="L91" s="5">
-        <v>11.10458710114142</v>
+        <v>44.8849205259704</v>
       </c>
       <c r="M91" s="5">
-        <v>18.35079858233862</v>
+        <v>30.7156576212915</v>
       </c>
       <c r="N91" s="5">
-        <v>17.22062131075827</v>
+        <v>39.25996577576155</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4770,43 +4806,43 @@
         <v>102</v>
       </c>
       <c r="B92" s="4">
-        <v>0</v>
+        <v>11858.95</v>
       </c>
       <c r="C92" s="4">
-        <v>0</v>
+        <v>23110.93</v>
       </c>
       <c r="D92" s="4">
-        <v>0</v>
+        <v>14276.03</v>
       </c>
       <c r="E92" s="4">
-        <v>0</v>
+        <v>151264.33</v>
       </c>
       <c r="F92" s="4">
-        <v>0</v>
+        <v>242510.64</v>
       </c>
       <c r="G92" s="4">
-        <v>0</v>
+        <v>228933.08</v>
       </c>
       <c r="H92" s="4">
-        <v>0</v>
+        <v>228933.08</v>
       </c>
       <c r="I92" s="4">
-        <v>0</v>
+        <v>69990.73</v>
       </c>
       <c r="J92" s="4">
-        <v>0</v>
+        <v>104084.68</v>
       </c>
       <c r="K92" s="4">
-        <v>0</v>
+        <v>80495.28999999999</v>
       </c>
       <c r="L92" s="4">
-        <v>804.4400000000001</v>
+        <v>391967.57</v>
       </c>
       <c r="M92" s="4">
-        <v>42000</v>
+        <v>617864.85</v>
       </c>
       <c r="N92" s="4">
-        <v>1670</v>
+        <v>606194.52</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4814,43 +4850,43 @@
         <v>103</v>
       </c>
       <c r="B93" s="4">
-        <v>201.2</v>
+        <v>2356.6277</v>
       </c>
       <c r="C93" s="4">
-        <v>201.25</v>
+        <v>3770.7</v>
       </c>
       <c r="D93" s="4">
-        <v>195.88</v>
+        <v>2349.82</v>
       </c>
       <c r="E93" s="4">
-        <v>1408.4</v>
+        <v>19843.56455833334</v>
       </c>
       <c r="F93" s="4">
-        <v>1408.75</v>
+        <v>26319.7</v>
       </c>
       <c r="G93" s="4">
-        <v>1371.16</v>
+        <v>23127.37</v>
       </c>
       <c r="H93" s="4">
-        <v>1371.16</v>
+        <v>23127.37</v>
       </c>
       <c r="I93" s="4">
-        <v>804.8</v>
+        <v>10831.56358055556</v>
       </c>
       <c r="J93" s="4">
-        <v>805</v>
+        <v>15052</v>
       </c>
       <c r="K93" s="4">
-        <v>783.52</v>
+        <v>13806.57</v>
       </c>
       <c r="L93" s="4">
-        <v>13078</v>
+        <v>97845.70983055566</v>
       </c>
       <c r="M93" s="4">
-        <v>13081.25</v>
+        <v>121533.42</v>
       </c>
       <c r="N93" s="4">
-        <v>12933.5</v>
+        <v>105979.34</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4858,43 +4894,43 @@
         <v>104</v>
       </c>
       <c r="B94" s="5">
-        <v>0</v>
+        <v>19.87214466710796</v>
       </c>
       <c r="C94" s="5">
-        <v>0</v>
+        <v>16.31565670442513</v>
       </c>
       <c r="D94" s="5">
-        <v>0</v>
+        <v>16.45989816496603</v>
       </c>
       <c r="E94" s="5">
-        <v>0</v>
+        <v>13.11846921103828</v>
       </c>
       <c r="F94" s="5">
-        <v>0</v>
+        <v>10.85300834635544</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>10.10224035774996</v>
       </c>
       <c r="H94" s="5">
-        <v>0</v>
+        <v>10.10224035774996</v>
       </c>
       <c r="I94" s="5">
-        <v>0</v>
+        <v>15.47571168432671</v>
       </c>
       <c r="J94" s="5">
-        <v>0</v>
+        <v>14.4613020859554</v>
       </c>
       <c r="K94" s="5">
-        <v>0</v>
+        <v>17.15202218663974</v>
       </c>
       <c r="L94" s="5">
-        <v>1625.727213962508</v>
+        <v>24.96270541732716</v>
       </c>
       <c r="M94" s="5">
-        <v>31.14583333333333</v>
+        <v>19.66990353958475</v>
       </c>
       <c r="N94" s="5">
-        <v>774.4610778443114</v>
+        <v>17.48272815135313</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4902,43 +4938,43 @@
         <v>105</v>
       </c>
       <c r="B95" s="4">
-        <v>0</v>
+        <v>2225.97</v>
       </c>
       <c r="C95" s="4">
-        <v>0</v>
+        <v>3938.41</v>
       </c>
       <c r="D95" s="4">
-        <v>0</v>
+        <v>2794.51</v>
       </c>
       <c r="E95" s="4">
-        <v>0</v>
+        <v>37855.59</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>33077.08</v>
       </c>
       <c r="G95" s="4">
-        <v>0</v>
+        <v>46171.39</v>
       </c>
       <c r="H95" s="4">
-        <v>0</v>
+        <v>46171.39</v>
       </c>
       <c r="I95" s="4">
-        <v>0</v>
+        <v>17077.99</v>
       </c>
       <c r="J95" s="4">
-        <v>0</v>
+        <v>17737.37</v>
       </c>
       <c r="K95" s="4">
-        <v>0</v>
+        <v>19416.46</v>
       </c>
       <c r="L95" s="4">
-        <v>0</v>
+        <v>101728.76</v>
       </c>
       <c r="M95" s="4">
-        <v>0</v>
+        <v>98883.98</v>
       </c>
       <c r="N95" s="4">
-        <v>0</v>
+        <v>89479.92</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4946,43 +4982,43 @@
         <v>106</v>
       </c>
       <c r="B96" s="4">
-        <v>594.23</v>
+        <v>262.0532333333333</v>
       </c>
       <c r="C96" s="4">
-        <v>594.37</v>
+        <v>404.55</v>
       </c>
       <c r="D96" s="4">
-        <v>578.51</v>
+        <v>483.14</v>
       </c>
       <c r="E96" s="4">
-        <v>4159.61</v>
+        <v>1976.845822222222</v>
       </c>
       <c r="F96" s="4">
-        <v>4160.59</v>
+        <v>2883.65</v>
       </c>
       <c r="G96" s="4">
-        <v>4049.57</v>
+        <v>2805.62</v>
       </c>
       <c r="H96" s="4">
-        <v>4049.57</v>
+        <v>2805.62</v>
       </c>
       <c r="I96" s="4">
-        <v>2376.92</v>
+        <v>1015.387322222222</v>
       </c>
       <c r="J96" s="4">
-        <v>2377.48</v>
+        <v>1644.1</v>
       </c>
       <c r="K96" s="4">
-        <v>2314.04</v>
+        <v>1518.14</v>
       </c>
       <c r="L96" s="4">
-        <v>40009.99299999999</v>
+        <v>11296.55876111112</v>
       </c>
       <c r="M96" s="4">
-        <v>38634.05</v>
+        <v>18146</v>
       </c>
       <c r="N96" s="4">
-        <v>37603.15</v>
+        <v>13640.17</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4990,43 +5026,43 @@
         <v>107</v>
       </c>
       <c r="B97" s="5">
-        <v>0</v>
+        <v>11.77254110941896</v>
       </c>
       <c r="C97" s="5">
-        <v>0</v>
+        <v>10.27191176134532</v>
       </c>
       <c r="D97" s="5">
-        <v>0</v>
+        <v>17.28889859045056</v>
       </c>
       <c r="E97" s="5">
-        <v>0</v>
+        <v>5.222071092333318</v>
       </c>
       <c r="F97" s="5">
-        <v>0</v>
+        <v>8.717970268234076</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>6.076533541658589</v>
       </c>
       <c r="H97" s="5">
-        <v>0</v>
+        <v>6.076533541658589</v>
       </c>
       <c r="I97" s="5">
-        <v>0</v>
+        <v>5.945590331310781</v>
       </c>
       <c r="J97" s="5">
-        <v>0</v>
+        <v>9.269130654657371</v>
       </c>
       <c r="K97" s="5">
-        <v>0</v>
+        <v>7.818830002997458</v>
       </c>
       <c r="L97" s="5">
-        <v>0</v>
+        <v>11.10458710114142</v>
       </c>
       <c r="M97" s="5">
-        <v>0</v>
+        <v>18.35079858233862</v>
       </c>
       <c r="N97" s="5">
-        <v>0</v>
+        <v>15.24383347682922</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -5049,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="G98" s="4">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H98" s="4">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I98" s="4">
         <v>0</v>
@@ -5061,16 +5097,16 @@
         <v>0</v>
       </c>
       <c r="K98" s="4">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="L98" s="4">
-        <v>0</v>
+        <v>804.4400000000001</v>
       </c>
       <c r="M98" s="4">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="N98" s="4">
-        <v>0</v>
+        <v>48830</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -5078,43 +5114,43 @@
         <v>109</v>
       </c>
       <c r="B99" s="4">
-        <v>0</v>
+        <v>201.2</v>
       </c>
       <c r="C99" s="4">
-        <v>0</v>
+        <v>201.25</v>
       </c>
       <c r="D99" s="4">
-        <v>0</v>
+        <v>195.88</v>
       </c>
       <c r="E99" s="4">
-        <v>0</v>
+        <v>1408.4</v>
       </c>
       <c r="F99" s="4">
-        <v>0</v>
+        <v>1408.75</v>
       </c>
       <c r="G99" s="4">
-        <v>0</v>
+        <v>1371.16</v>
       </c>
       <c r="H99" s="4">
-        <v>0</v>
+        <v>1371.16</v>
       </c>
       <c r="I99" s="4">
-        <v>0</v>
+        <v>804.8</v>
       </c>
       <c r="J99" s="4">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="K99" s="4">
-        <v>0</v>
+        <v>783.52</v>
       </c>
       <c r="L99" s="4">
-        <v>62.8375</v>
+        <v>13078</v>
       </c>
       <c r="M99" s="4">
-        <v>0</v>
+        <v>13081.25</v>
       </c>
       <c r="N99" s="4">
-        <v>0</v>
+        <v>12933.5</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -5137,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <v>0</v>
+        <v>11.42633333333333</v>
       </c>
       <c r="H100" s="5">
-        <v>0</v>
+        <v>11.42633333333333</v>
       </c>
       <c r="I100" s="5">
         <v>0</v>
@@ -5149,16 +5185,16 @@
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>0</v>
+        <v>6.529333333333333</v>
       </c>
       <c r="L100" s="5">
-        <v>0</v>
+        <v>1625.727213962508</v>
       </c>
       <c r="M100" s="5">
-        <v>0</v>
+        <v>30.42151162790698</v>
       </c>
       <c r="N100" s="5">
-        <v>0</v>
+        <v>26.48679090722916</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -5202,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -5210,43 +5246,43 @@
         <v>112</v>
       </c>
       <c r="B102" s="4">
-        <v>0</v>
+        <v>594.23</v>
       </c>
       <c r="C102" s="4">
-        <v>0</v>
+        <v>594.37</v>
       </c>
       <c r="D102" s="4">
-        <v>0</v>
+        <v>578.51</v>
       </c>
       <c r="E102" s="4">
-        <v>83.14458333333333</v>
+        <v>4159.61</v>
       </c>
       <c r="F102" s="4">
-        <v>0</v>
+        <v>4160.59</v>
       </c>
       <c r="G102" s="4">
-        <v>0</v>
+        <v>4049.57</v>
       </c>
       <c r="H102" s="4">
-        <v>0</v>
+        <v>4049.57</v>
       </c>
       <c r="I102" s="4">
-        <v>83.14458333333333</v>
+        <v>2376.92</v>
       </c>
       <c r="J102" s="4">
-        <v>0</v>
+        <v>2377.48</v>
       </c>
       <c r="K102" s="4">
-        <v>0</v>
+        <v>2314.04</v>
       </c>
       <c r="L102" s="4">
-        <v>676.4372222222222</v>
+        <v>40009.99299999999</v>
       </c>
       <c r="M102" s="4">
-        <v>0</v>
+        <v>38634.05</v>
       </c>
       <c r="N102" s="4">
-        <v>0</v>
+        <v>37603.15</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5290,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="5">
-        <v>0</v>
+        <v>12534.38333333333</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5301,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="C104" s="4">
-        <v>59717.96</v>
+        <v>0</v>
       </c>
       <c r="D104" s="4">
         <v>0</v>
@@ -5310,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="4">
-        <v>727244.71</v>
+        <v>0</v>
       </c>
       <c r="G104" s="4">
         <v>0</v>
@@ -5322,16 +5358,16 @@
         <v>0</v>
       </c>
       <c r="J104" s="4">
-        <v>271595.87</v>
+        <v>0</v>
       </c>
       <c r="K104" s="4">
         <v>0</v>
       </c>
       <c r="L104" s="4">
-        <v>620.78</v>
+        <v>0</v>
       </c>
       <c r="M104" s="4">
-        <v>1225819.88</v>
+        <v>0</v>
       </c>
       <c r="N104" s="4">
         <v>0</v>
@@ -5342,43 +5378,43 @@
         <v>115</v>
       </c>
       <c r="B105" s="4">
-        <v>1107.903777777778</v>
+        <v>0</v>
       </c>
       <c r="C105" s="4">
-        <v>1854.08</v>
+        <v>0</v>
       </c>
       <c r="D105" s="4">
-        <v>1887.25</v>
+        <v>0</v>
       </c>
       <c r="E105" s="4">
-        <v>8350.396577777778</v>
+        <v>0</v>
       </c>
       <c r="F105" s="4">
-        <v>12138.26</v>
+        <v>0</v>
       </c>
       <c r="G105" s="4">
-        <v>14340.28</v>
+        <v>0</v>
       </c>
       <c r="H105" s="4">
-        <v>14340.28</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4">
-        <v>4904.065555555556</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4">
-        <v>7108.58</v>
+        <v>0</v>
       </c>
       <c r="K105" s="4">
-        <v>8054.45</v>
+        <v>0</v>
       </c>
       <c r="L105" s="4">
-        <v>80166.56015277776</v>
+        <v>62.8375</v>
       </c>
       <c r="M105" s="4">
-        <v>100942.9</v>
+        <v>0</v>
       </c>
       <c r="N105" s="4">
-        <v>112595.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5389,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="C106" s="5">
-        <v>3.104727622979754</v>
+        <v>0</v>
       </c>
       <c r="D106" s="5">
         <v>0</v>
@@ -5398,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="5">
-        <v>1.66907504902992</v>
+        <v>0</v>
       </c>
       <c r="G106" s="5">
         <v>0</v>
@@ -5410,16 +5446,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="5">
-        <v>2.61733729603473</v>
+        <v>0</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
       </c>
       <c r="L106" s="5">
-        <v>12913.84389844675</v>
+        <v>0</v>
       </c>
       <c r="M106" s="5">
-        <v>8.234725317066975</v>
+        <v>0</v>
       </c>
       <c r="N106" s="5">
         <v>0</v>
@@ -5442,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="4">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="G107" s="4">
         <v>0</v>
@@ -5463,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="4">
-        <v>134000</v>
+        <v>0</v>
       </c>
       <c r="N107" s="4">
         <v>0</v>
@@ -5474,43 +5510,43 @@
         <v>118</v>
       </c>
       <c r="B108" s="4">
-        <v>488.7094222222223</v>
+        <v>0</v>
       </c>
       <c r="C108" s="4">
-        <v>414.08</v>
+        <v>0</v>
       </c>
       <c r="D108" s="4">
-        <v>942.15</v>
+        <v>0</v>
       </c>
       <c r="E108" s="4">
-        <v>4671.676899999999</v>
+        <v>83.14458333333333</v>
       </c>
       <c r="F108" s="4">
-        <v>4008.69</v>
+        <v>0</v>
       </c>
       <c r="G108" s="4">
-        <v>4726.81</v>
+        <v>0</v>
       </c>
       <c r="H108" s="4">
-        <v>4726.81</v>
+        <v>0</v>
       </c>
       <c r="I108" s="4">
-        <v>2490.759041666667</v>
+        <v>83.14458333333333</v>
       </c>
       <c r="J108" s="4">
-        <v>2066.58</v>
+        <v>0</v>
       </c>
       <c r="K108" s="4">
-        <v>2420.66</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4">
-        <v>28552.66472777777</v>
+        <v>676.4372222222222</v>
       </c>
       <c r="M108" s="4">
-        <v>31162.69</v>
+        <v>0</v>
       </c>
       <c r="N108" s="4">
-        <v>32594.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5530,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="5">
-        <v>32.06952</v>
+        <v>0</v>
       </c>
       <c r="G109" s="5">
         <v>0</v>
@@ -5551,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="5">
-        <v>23.25573880597015</v>
+        <v>0</v>
       </c>
       <c r="N109" s="5">
         <v>0</v>
@@ -5565,40 +5601,40 @@
         <v>0</v>
       </c>
       <c r="C110" s="4">
-        <v>0</v>
+        <v>94432.89999999999</v>
       </c>
       <c r="D110" s="4">
-        <v>0</v>
+        <v>54891.73</v>
       </c>
       <c r="E110" s="4">
         <v>0</v>
       </c>
       <c r="F110" s="4">
-        <v>0</v>
+        <v>1151970.37</v>
       </c>
       <c r="G110" s="4">
-        <v>0</v>
+        <v>867005.22</v>
       </c>
       <c r="H110" s="4">
-        <v>0</v>
+        <v>867005.22</v>
       </c>
       <c r="I110" s="4">
         <v>0</v>
       </c>
       <c r="J110" s="4">
-        <v>0</v>
+        <v>429686.8</v>
       </c>
       <c r="K110" s="4">
-        <v>0</v>
+        <v>290126.88</v>
       </c>
       <c r="L110" s="4">
-        <v>0</v>
+        <v>620.78</v>
       </c>
       <c r="M110" s="4">
-        <v>0</v>
+        <v>1921508.32</v>
       </c>
       <c r="N110" s="4">
-        <v>0</v>
+        <v>1574508.34</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5606,43 +5642,43 @@
         <v>121</v>
       </c>
       <c r="B111" s="4">
-        <v>1230.52</v>
+        <v>1107.903777777778</v>
       </c>
       <c r="C111" s="4">
-        <v>313.93</v>
+        <v>1854.08</v>
       </c>
       <c r="D111" s="4">
-        <v>1287.88</v>
+        <v>1887.25</v>
       </c>
       <c r="E111" s="4">
-        <v>9459.619627777776</v>
+        <v>8350.396577777778</v>
       </c>
       <c r="F111" s="4">
-        <v>3103.91</v>
+        <v>12138.26</v>
       </c>
       <c r="G111" s="4">
-        <v>9721.719999999999</v>
+        <v>14340.28</v>
       </c>
       <c r="H111" s="4">
-        <v>9721.719999999999</v>
+        <v>14340.28</v>
       </c>
       <c r="I111" s="4">
-        <v>5202.799633333333</v>
+        <v>4904.065555555555</v>
       </c>
       <c r="J111" s="4">
-        <v>1618.28</v>
+        <v>7108.58</v>
       </c>
       <c r="K111" s="4">
-        <v>5494.28</v>
+        <v>8054.45</v>
       </c>
       <c r="L111" s="4">
-        <v>88036.45902222222</v>
+        <v>80166.56015277776</v>
       </c>
       <c r="M111" s="4">
-        <v>28563.05</v>
+        <v>100942.9</v>
       </c>
       <c r="N111" s="4">
-        <v>98364.24000000001</v>
+        <v>112595.49</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5653,40 +5689,40 @@
         <v>0</v>
       </c>
       <c r="C112" s="5">
-        <v>0</v>
+        <v>1.963383524174308</v>
       </c>
       <c r="D112" s="5">
-        <v>0</v>
+        <v>3.438131755002074</v>
       </c>
       <c r="E112" s="5">
         <v>0</v>
       </c>
       <c r="F112" s="5">
-        <v>0</v>
+        <v>1.053695504338362</v>
       </c>
       <c r="G112" s="5">
-        <v>0</v>
+        <v>1.654001575676788</v>
       </c>
       <c r="H112" s="5">
-        <v>0</v>
+        <v>1.654001575676788</v>
       </c>
       <c r="I112" s="5">
         <v>0</v>
       </c>
       <c r="J112" s="5">
-        <v>0</v>
+        <v>1.654363131471574</v>
       </c>
       <c r="K112" s="5">
-        <v>0</v>
+        <v>2.776181924267065</v>
       </c>
       <c r="L112" s="5">
-        <v>0</v>
+        <v>12913.84389844675</v>
       </c>
       <c r="M112" s="5">
-        <v>0</v>
+        <v>5.253315791003184</v>
       </c>
       <c r="N112" s="5">
-        <v>0</v>
+        <v>7.151152340037779</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5697,40 +5733,40 @@
         <v>0</v>
       </c>
       <c r="C113" s="4">
-        <v>1745.45</v>
+        <v>0</v>
       </c>
       <c r="D113" s="4">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="E113" s="4">
         <v>0</v>
       </c>
       <c r="F113" s="4">
-        <v>12218.15</v>
+        <v>12500</v>
       </c>
       <c r="G113" s="4">
-        <v>0</v>
+        <v>27105</v>
       </c>
       <c r="H113" s="4">
-        <v>0</v>
+        <v>27105</v>
       </c>
       <c r="I113" s="4">
         <v>0</v>
       </c>
       <c r="J113" s="4">
-        <v>6981.8</v>
+        <v>0</v>
       </c>
       <c r="K113" s="4">
-        <v>0</v>
+        <v>4140</v>
       </c>
       <c r="L113" s="4">
         <v>0</v>
       </c>
       <c r="M113" s="4">
-        <v>113454.25</v>
+        <v>134000</v>
       </c>
       <c r="N113" s="4">
-        <v>0</v>
+        <v>139078.73</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5738,43 +5774,43 @@
         <v>124</v>
       </c>
       <c r="B114" s="4">
-        <v>368.46</v>
+        <v>488.7094222222223</v>
       </c>
       <c r="C114" s="4">
-        <v>1190.63</v>
+        <v>414.08</v>
       </c>
       <c r="D114" s="4">
-        <v>354.62</v>
+        <v>942.15</v>
       </c>
       <c r="E114" s="4">
-        <v>2579.22</v>
+        <v>4671.6769</v>
       </c>
       <c r="F114" s="4">
-        <v>8334.41</v>
+        <v>4008.69</v>
       </c>
       <c r="G114" s="4">
-        <v>2482.34</v>
+        <v>4726.81</v>
       </c>
       <c r="H114" s="4">
-        <v>2482.34</v>
+        <v>4726.81</v>
       </c>
       <c r="I114" s="4">
-        <v>1473.84</v>
+        <v>2490.759041666667</v>
       </c>
       <c r="J114" s="4">
-        <v>4762.52</v>
+        <v>2066.58</v>
       </c>
       <c r="K114" s="4">
-        <v>1418.48</v>
+        <v>2420.66</v>
       </c>
       <c r="L114" s="4">
-        <v>23949.9</v>
+        <v>28552.66472777776</v>
       </c>
       <c r="M114" s="4">
-        <v>77390.95</v>
+        <v>31162.69</v>
       </c>
       <c r="N114" s="4">
-        <v>23050.3</v>
+        <v>32594.46</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5785,40 +5821,40 @@
         <v>0</v>
       </c>
       <c r="C115" s="5">
-        <v>68.21335472227793</v>
+        <v>0</v>
       </c>
       <c r="D115" s="5">
-        <v>0</v>
+        <v>82.28384279475982</v>
       </c>
       <c r="E115" s="5">
         <v>0</v>
       </c>
       <c r="F115" s="5">
-        <v>68.21335472227791</v>
+        <v>32.06952</v>
       </c>
       <c r="G115" s="5">
-        <v>0</v>
+        <v>17.43888581442538</v>
       </c>
       <c r="H115" s="5">
-        <v>0</v>
+        <v>17.43888581442538</v>
       </c>
       <c r="I115" s="5">
         <v>0</v>
       </c>
       <c r="J115" s="5">
-        <v>68.21335472227793</v>
+        <v>0</v>
       </c>
       <c r="K115" s="5">
-        <v>0</v>
+        <v>58.47004830917874</v>
       </c>
       <c r="L115" s="5">
         <v>0</v>
       </c>
       <c r="M115" s="5">
-        <v>68.21335472227791</v>
+        <v>23.25573880597015</v>
       </c>
       <c r="N115" s="5">
-        <v>0</v>
+        <v>23.43597759341058</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5826,43 +5862,43 @@
         <v>126</v>
       </c>
       <c r="B116" s="4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C116" s="4">
-        <v>1858.7</v>
+        <v>720.12</v>
       </c>
       <c r="D116" s="4">
-        <v>300</v>
+        <v>625.95</v>
       </c>
       <c r="E116" s="4">
-        <v>15968.25</v>
+        <v>0</v>
       </c>
       <c r="F116" s="4">
-        <v>16439</v>
+        <v>5040.84</v>
       </c>
       <c r="G116" s="4">
-        <v>13905</v>
+        <v>26036.1</v>
       </c>
       <c r="H116" s="4">
-        <v>13905</v>
+        <v>26036.1</v>
       </c>
       <c r="I116" s="4">
-        <v>4460</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4">
-        <v>8644.1</v>
+        <v>2880.48</v>
       </c>
       <c r="K116" s="4">
-        <v>8310</v>
+        <v>2503.8</v>
       </c>
       <c r="L116" s="4">
-        <v>23078.25</v>
+        <v>0</v>
       </c>
       <c r="M116" s="4">
-        <v>45736.6</v>
+        <v>46807.8</v>
       </c>
       <c r="N116" s="4">
-        <v>27765</v>
+        <v>85621.38</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5870,43 +5906,43 @@
         <v>127</v>
       </c>
       <c r="B117" s="4">
-        <v>389.08</v>
+        <v>1230.52</v>
       </c>
       <c r="C117" s="4">
-        <v>391.37</v>
+        <v>313.93</v>
       </c>
       <c r="D117" s="4">
-        <v>493.12</v>
+        <v>1287.88</v>
       </c>
       <c r="E117" s="4">
-        <v>2723.56</v>
+        <v>9459.619627777776</v>
       </c>
       <c r="F117" s="4">
-        <v>2739.59</v>
+        <v>3103.91</v>
       </c>
       <c r="G117" s="4">
-        <v>3285.93</v>
+        <v>9721.719999999999</v>
       </c>
       <c r="H117" s="4">
-        <v>3285.93</v>
+        <v>9721.719999999999</v>
       </c>
       <c r="I117" s="4">
-        <v>1556.32</v>
+        <v>5202.799633333333</v>
       </c>
       <c r="J117" s="4">
-        <v>1565.48</v>
+        <v>1618.28</v>
       </c>
       <c r="K117" s="4">
-        <v>2030.97</v>
+        <v>5494.28</v>
       </c>
       <c r="L117" s="4">
-        <v>25477.13333333334</v>
+        <v>88036.45902222223</v>
       </c>
       <c r="M117" s="4">
-        <v>25439.05</v>
+        <v>28563.05</v>
       </c>
       <c r="N117" s="4">
-        <v>35032.33</v>
+        <v>98364.24000000001</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5914,43 +5950,43 @@
         <v>128</v>
       </c>
       <c r="B118" s="5">
-        <v>32.42333333333333</v>
+        <v>0</v>
       </c>
       <c r="C118" s="5">
-        <v>21.05611448862108</v>
+        <v>43.5941232016886</v>
       </c>
       <c r="D118" s="5">
-        <v>164.3733333333333</v>
+        <v>205.7480629443246</v>
       </c>
       <c r="E118" s="5">
-        <v>17.05609568988461</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5">
-        <v>16.66518644686417</v>
+        <v>61.57525333079407</v>
       </c>
       <c r="G118" s="5">
-        <v>23.63128371089536</v>
+        <v>37.33938646725124</v>
       </c>
       <c r="H118" s="5">
-        <v>23.63128371089536</v>
+        <v>37.33938646725124</v>
       </c>
       <c r="I118" s="5">
-        <v>34.895067264574</v>
+        <v>0</v>
       </c>
       <c r="J118" s="5">
-        <v>18.11038743188996</v>
+        <v>56.18091429206243</v>
       </c>
       <c r="K118" s="5">
-        <v>24.44007220216607</v>
+        <v>219.4376547647576</v>
       </c>
       <c r="L118" s="5">
-        <v>110.3945634237143</v>
+        <v>0</v>
       </c>
       <c r="M118" s="5">
-        <v>55.62077198567449</v>
+        <v>61.02198778836006</v>
       </c>
       <c r="N118" s="5">
-        <v>126.174428236989</v>
+        <v>114.8828014685117</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5961,40 +5997,40 @@
         <v>0</v>
       </c>
       <c r="C119" s="4">
-        <v>0</v>
+        <v>1745.45</v>
       </c>
       <c r="D119" s="4">
-        <v>0</v>
+        <v>1533.34</v>
       </c>
       <c r="E119" s="4">
         <v>0</v>
       </c>
       <c r="F119" s="4">
-        <v>0</v>
+        <v>12218.15</v>
       </c>
       <c r="G119" s="4">
-        <v>0</v>
+        <v>136024</v>
       </c>
       <c r="H119" s="4">
-        <v>0</v>
+        <v>136024</v>
       </c>
       <c r="I119" s="4">
         <v>0</v>
       </c>
       <c r="J119" s="4">
-        <v>0</v>
+        <v>6981.8</v>
       </c>
       <c r="K119" s="4">
-        <v>0</v>
+        <v>6133.36</v>
       </c>
       <c r="L119" s="4">
         <v>0</v>
       </c>
       <c r="M119" s="4">
-        <v>0</v>
+        <v>113454.25</v>
       </c>
       <c r="N119" s="4">
-        <v>0</v>
+        <v>426925.66</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -6002,43 +6038,43 @@
         <v>130</v>
       </c>
       <c r="B120" s="4">
-        <v>0</v>
+        <v>368.46</v>
       </c>
       <c r="C120" s="4">
-        <v>0</v>
+        <v>1190.63</v>
       </c>
       <c r="D120" s="4">
-        <v>0</v>
+        <v>354.62</v>
       </c>
       <c r="E120" s="4">
-        <v>0</v>
+        <v>2579.22</v>
       </c>
       <c r="F120" s="4">
-        <v>0</v>
+        <v>8334.41</v>
       </c>
       <c r="G120" s="4">
-        <v>0</v>
+        <v>2482.34</v>
       </c>
       <c r="H120" s="4">
-        <v>0</v>
+        <v>2482.34</v>
       </c>
       <c r="I120" s="4">
-        <v>0</v>
+        <v>1473.84</v>
       </c>
       <c r="J120" s="4">
-        <v>0</v>
+        <v>4762.52</v>
       </c>
       <c r="K120" s="4">
-        <v>0</v>
+        <v>1418.48</v>
       </c>
       <c r="L120" s="4">
-        <v>0</v>
+        <v>23949.9</v>
       </c>
       <c r="M120" s="4">
-        <v>0</v>
+        <v>77390.95</v>
       </c>
       <c r="N120" s="4">
-        <v>1332.54</v>
+        <v>23050.3</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -6049,40 +6085,40 @@
         <v>0</v>
       </c>
       <c r="C121" s="5">
-        <v>0</v>
+        <v>68.21335472227793</v>
       </c>
       <c r="D121" s="5">
-        <v>0</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="E121" s="5">
         <v>0</v>
       </c>
       <c r="F121" s="5">
-        <v>0</v>
+        <v>68.21335472227791</v>
       </c>
       <c r="G121" s="5">
-        <v>0</v>
+        <v>1.82492795389049</v>
       </c>
       <c r="H121" s="5">
-        <v>0</v>
+        <v>1.82492795389049</v>
       </c>
       <c r="I121" s="5">
         <v>0</v>
       </c>
       <c r="J121" s="5">
-        <v>0</v>
+        <v>68.21335472227793</v>
       </c>
       <c r="K121" s="5">
-        <v>0</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="L121" s="5">
         <v>0</v>
       </c>
       <c r="M121" s="5">
-        <v>0</v>
+        <v>68.21335472227791</v>
       </c>
       <c r="N121" s="5">
-        <v>0</v>
+        <v>5.399136702160278</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6090,43 +6126,43 @@
         <v>132</v>
       </c>
       <c r="B122" s="4">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C122" s="4">
-        <v>221.25</v>
+        <v>1858.7</v>
       </c>
       <c r="D122" s="4">
         <v>0</v>
       </c>
       <c r="E122" s="4">
-        <v>0</v>
+        <v>15968.25</v>
       </c>
       <c r="F122" s="4">
-        <v>1548.75</v>
+        <v>16439</v>
       </c>
       <c r="G122" s="4">
-        <v>0</v>
+        <v>16451.25</v>
       </c>
       <c r="H122" s="4">
-        <v>0</v>
+        <v>16451.25</v>
       </c>
       <c r="I122" s="4">
-        <v>0</v>
+        <v>4460</v>
       </c>
       <c r="J122" s="4">
-        <v>885</v>
+        <v>8644.1</v>
       </c>
       <c r="K122" s="4">
-        <v>0</v>
+        <v>2340</v>
       </c>
       <c r="L122" s="4">
-        <v>0</v>
+        <v>23078.25</v>
       </c>
       <c r="M122" s="4">
-        <v>14381.25</v>
+        <v>45736.6</v>
       </c>
       <c r="N122" s="4">
-        <v>0</v>
+        <v>20872.97</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6134,43 +6170,43 @@
         <v>133</v>
       </c>
       <c r="B123" s="4">
-        <v>0</v>
+        <v>389.08</v>
       </c>
       <c r="C123" s="4">
-        <v>180</v>
+        <v>391.37</v>
       </c>
       <c r="D123" s="4">
-        <v>178.13</v>
+        <v>493.12</v>
       </c>
       <c r="E123" s="4">
-        <v>993.9172222222223</v>
+        <v>2723.56</v>
       </c>
       <c r="F123" s="4">
-        <v>1322.8</v>
+        <v>2739.59</v>
       </c>
       <c r="G123" s="4">
-        <v>1419.36</v>
+        <v>3285.93</v>
       </c>
       <c r="H123" s="4">
-        <v>1419.36</v>
+        <v>3285.93</v>
       </c>
       <c r="I123" s="4">
-        <v>451.1022222222222</v>
+        <v>1556.32</v>
       </c>
       <c r="J123" s="4">
-        <v>767.1</v>
+        <v>1565.48</v>
       </c>
       <c r="K123" s="4">
-        <v>676.13</v>
+        <v>2030.97</v>
       </c>
       <c r="L123" s="4">
-        <v>9444.90478333333</v>
+        <v>25477.13333333334</v>
       </c>
       <c r="M123" s="4">
-        <v>12280.9</v>
+        <v>25439.05</v>
       </c>
       <c r="N123" s="4">
-        <v>12728.76</v>
+        <v>35032.33</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -6178,43 +6214,43 @@
         <v>134</v>
       </c>
       <c r="B124" s="5">
-        <v>0</v>
+        <v>32.42333333333333</v>
       </c>
       <c r="C124" s="5">
-        <v>81.35593220338984</v>
+        <v>21.05611448862108</v>
       </c>
       <c r="D124" s="5">
         <v>0</v>
       </c>
       <c r="E124" s="5">
-        <v>0</v>
+        <v>17.05609568988461</v>
       </c>
       <c r="F124" s="5">
-        <v>85.41081517352703</v>
+        <v>16.66518644686417</v>
       </c>
       <c r="G124" s="5">
-        <v>0</v>
+        <v>19.97374059721906</v>
       </c>
       <c r="H124" s="5">
-        <v>0</v>
+        <v>19.97374059721906</v>
       </c>
       <c r="I124" s="5">
-        <v>0</v>
+        <v>34.895067264574</v>
       </c>
       <c r="J124" s="5">
-        <v>86.67796610169492</v>
+        <v>18.11038743188996</v>
       </c>
       <c r="K124" s="5">
-        <v>0</v>
+        <v>86.79358974358975</v>
       </c>
       <c r="L124" s="5">
-        <v>0</v>
+        <v>110.3945634237143</v>
       </c>
       <c r="M124" s="5">
-        <v>85.39521946979573</v>
+        <v>55.62077198567449</v>
       </c>
       <c r="N124" s="5">
-        <v>0</v>
+        <v>167.8358661944131</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6225,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="4">
-        <v>1314.68</v>
+        <v>0</v>
       </c>
       <c r="D125" s="4">
         <v>0</v>
@@ -6234,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="4">
-        <v>9202.76</v>
+        <v>0</v>
       </c>
       <c r="G125" s="4">
         <v>0</v>
@@ -6246,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="4">
-        <v>5258.72</v>
+        <v>0</v>
       </c>
       <c r="K125" s="4">
         <v>0</v>
@@ -6255,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="4">
-        <v>85454.2</v>
+        <v>0</v>
       </c>
       <c r="N125" s="4">
         <v>0</v>
@@ -6266,43 +6302,43 @@
         <v>136</v>
       </c>
       <c r="B126" s="4">
-        <v>938.3372222222222</v>
+        <v>0</v>
       </c>
       <c r="C126" s="4">
-        <v>936.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="D126" s="4">
-        <v>443.91</v>
+        <v>0</v>
       </c>
       <c r="E126" s="4">
-        <v>7787.580388888888</v>
+        <v>0</v>
       </c>
       <c r="F126" s="4">
-        <v>7470.03</v>
+        <v>0</v>
       </c>
       <c r="G126" s="4">
-        <v>5051.02</v>
+        <v>0</v>
       </c>
       <c r="H126" s="4">
-        <v>5051.02</v>
+        <v>0</v>
       </c>
       <c r="I126" s="4">
-        <v>4369.5028</v>
+        <v>0</v>
       </c>
       <c r="J126" s="4">
-        <v>4317.16</v>
+        <v>0</v>
       </c>
       <c r="K126" s="4">
-        <v>3370.04</v>
+        <v>0</v>
       </c>
       <c r="L126" s="4">
-        <v>68402.12267777773</v>
+        <v>0</v>
       </c>
       <c r="M126" s="4">
-        <v>66314.45</v>
+        <v>0</v>
       </c>
       <c r="N126" s="4">
-        <v>46170.49</v>
+        <v>1332.54</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6313,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="C127" s="5">
-        <v>71.24851674932303</v>
+        <v>0</v>
       </c>
       <c r="D127" s="5">
         <v>0</v>
@@ -6322,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="5">
-        <v>81.17162677283771</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
@@ -6334,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="5">
-        <v>82.09526272553016</v>
+        <v>0</v>
       </c>
       <c r="K127" s="5">
         <v>0</v>
@@ -6343,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="5">
-        <v>77.60232966899227</v>
+        <v>0</v>
       </c>
       <c r="N127" s="5">
         <v>0</v>
@@ -6357,40 +6393,40 @@
         <v>0</v>
       </c>
       <c r="C128" s="4">
-        <v>536.71</v>
+        <v>221.25</v>
       </c>
       <c r="D128" s="4">
-        <v>0</v>
+        <v>210.96</v>
       </c>
       <c r="E128" s="4">
         <v>0</v>
       </c>
       <c r="F128" s="4">
-        <v>16516.97</v>
+        <v>1548.75</v>
       </c>
       <c r="G128" s="4">
-        <v>960</v>
+        <v>20849.82</v>
       </c>
       <c r="H128" s="4">
-        <v>960</v>
+        <v>20849.82</v>
       </c>
       <c r="I128" s="4">
         <v>0</v>
       </c>
       <c r="J128" s="4">
-        <v>2146.84</v>
+        <v>885</v>
       </c>
       <c r="K128" s="4">
-        <v>160</v>
+        <v>843.84</v>
       </c>
       <c r="L128" s="4">
         <v>0</v>
       </c>
       <c r="M128" s="4">
-        <v>39986.15</v>
+        <v>14381.25</v>
       </c>
       <c r="N128" s="4">
-        <v>2720</v>
+        <v>58664.31</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6398,43 +6434,43 @@
         <v>139</v>
       </c>
       <c r="B129" s="4">
-        <v>2242.025222222223</v>
+        <v>0</v>
       </c>
       <c r="C129" s="4">
-        <v>2733.85</v>
+        <v>180</v>
       </c>
       <c r="D129" s="4">
-        <v>2980.6</v>
+        <v>178.13</v>
       </c>
       <c r="E129" s="4">
-        <v>15817.99143888889</v>
+        <v>993.9172222222223</v>
       </c>
       <c r="F129" s="4">
-        <v>20139.7</v>
+        <v>1322.8</v>
       </c>
       <c r="G129" s="4">
-        <v>18378.84</v>
+        <v>1419.36</v>
       </c>
       <c r="H129" s="4">
-        <v>18378.84</v>
+        <v>1419.36</v>
       </c>
       <c r="I129" s="4">
-        <v>9337.742716666673</v>
+        <v>451.1022222222222</v>
       </c>
       <c r="J129" s="4">
-        <v>11398.4</v>
+        <v>767.1</v>
       </c>
       <c r="K129" s="4">
-        <v>10154.23</v>
+        <v>676.13</v>
       </c>
       <c r="L129" s="4">
-        <v>72899.35422222235</v>
+        <v>9444.90478333333</v>
       </c>
       <c r="M129" s="4">
-        <v>86587.2</v>
+        <v>12280.9</v>
       </c>
       <c r="N129" s="4">
-        <v>89497.60000000001</v>
+        <v>12728.76</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6445,40 +6481,40 @@
         <v>0</v>
       </c>
       <c r="C130" s="5">
-        <v>509.3719140690503</v>
+        <v>81.35593220338984</v>
       </c>
       <c r="D130" s="5">
-        <v>0</v>
+        <v>84.43780811528251</v>
       </c>
       <c r="E130" s="5">
         <v>0</v>
       </c>
       <c r="F130" s="5">
-        <v>121.9333812436543</v>
+        <v>85.41081517352703</v>
       </c>
       <c r="G130" s="5">
-        <v>1914.4625</v>
+        <v>6.807540784524758</v>
       </c>
       <c r="H130" s="5">
-        <v>1914.4625</v>
+        <v>6.807540784524758</v>
       </c>
       <c r="I130" s="5">
         <v>0</v>
       </c>
       <c r="J130" s="5">
-        <v>530.9384956494196</v>
+        <v>86.67796610169492</v>
       </c>
       <c r="K130" s="5">
-        <v>6346.39375</v>
+        <v>80.12537921880924</v>
       </c>
       <c r="L130" s="5">
         <v>0</v>
       </c>
       <c r="M130" s="5">
-        <v>216.5429780061346</v>
+        <v>85.39521946979573</v>
       </c>
       <c r="N130" s="5">
-        <v>3290.352941176471</v>
+        <v>21.69762160332236</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6489,40 +6525,40 @@
         <v>0</v>
       </c>
       <c r="C131" s="4">
-        <v>0</v>
+        <v>1635.79</v>
       </c>
       <c r="D131" s="4">
-        <v>0</v>
+        <v>665.41</v>
       </c>
       <c r="E131" s="4">
         <v>0</v>
       </c>
       <c r="F131" s="4">
-        <v>0</v>
+        <v>11450.53</v>
       </c>
       <c r="G131" s="4">
-        <v>0</v>
+        <v>61630.29</v>
       </c>
       <c r="H131" s="4">
-        <v>0</v>
+        <v>61630.29</v>
       </c>
       <c r="I131" s="4">
         <v>0</v>
       </c>
       <c r="J131" s="4">
-        <v>0</v>
+        <v>6543.16</v>
       </c>
       <c r="K131" s="4">
-        <v>0</v>
+        <v>2661.64</v>
       </c>
       <c r="L131" s="4">
         <v>0</v>
       </c>
       <c r="M131" s="4">
-        <v>0</v>
+        <v>106326.35</v>
       </c>
       <c r="N131" s="4">
-        <v>0</v>
+        <v>190924.23</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6530,43 +6566,43 @@
         <v>142</v>
       </c>
       <c r="B132" s="4">
-        <v>0</v>
+        <v>938.3372222222222</v>
       </c>
       <c r="C132" s="4">
-        <v>0</v>
+        <v>936.6900000000001</v>
       </c>
       <c r="D132" s="4">
-        <v>218.25</v>
+        <v>443.91</v>
       </c>
       <c r="E132" s="4">
-        <v>0</v>
+        <v>7787.580388888889</v>
       </c>
       <c r="F132" s="4">
-        <v>0</v>
+        <v>7470.03</v>
       </c>
       <c r="G132" s="4">
-        <v>436.25</v>
+        <v>5051.02</v>
       </c>
       <c r="H132" s="4">
-        <v>436.25</v>
+        <v>5051.02</v>
       </c>
       <c r="I132" s="4">
-        <v>0</v>
+        <v>4369.5028</v>
       </c>
       <c r="J132" s="4">
-        <v>0</v>
+        <v>4317.16</v>
       </c>
       <c r="K132" s="4">
-        <v>218</v>
+        <v>3370.04</v>
       </c>
       <c r="L132" s="4">
-        <v>716.1311111111111</v>
+        <v>68402.12267777778</v>
       </c>
       <c r="M132" s="4">
-        <v>0</v>
+        <v>66314.45</v>
       </c>
       <c r="N132" s="4">
-        <v>3672.26</v>
+        <v>46170.49</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6577,40 +6613,40 @@
         <v>0</v>
       </c>
       <c r="C133" s="5">
-        <v>0</v>
+        <v>57.26224026311446</v>
       </c>
       <c r="D133" s="5">
-        <v>0</v>
+        <v>66.71225259614374</v>
       </c>
       <c r="E133" s="5">
         <v>0</v>
       </c>
       <c r="F133" s="5">
-        <v>0</v>
+        <v>65.23741695799234</v>
       </c>
       <c r="G133" s="5">
-        <v>0</v>
+        <v>8.195677807130227</v>
       </c>
       <c r="H133" s="5">
-        <v>0</v>
+        <v>8.195677807130227</v>
       </c>
       <c r="I133" s="5">
         <v>0</v>
       </c>
       <c r="J133" s="5">
-        <v>0</v>
+        <v>65.97974067575912</v>
       </c>
       <c r="K133" s="5">
-        <v>0</v>
+        <v>126.615169594686</v>
       </c>
       <c r="L133" s="5">
         <v>0</v>
       </c>
       <c r="M133" s="5">
-        <v>0</v>
+        <v>62.36878252662675</v>
       </c>
       <c r="N133" s="5">
-        <v>0</v>
+        <v>24.18262469881376</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -6618,43 +6654,43 @@
         <v>144</v>
       </c>
       <c r="B134" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C134" s="4">
-        <v>863.28</v>
+        <v>536.71</v>
       </c>
       <c r="D134" s="4">
-        <v>0</v>
+        <v>448.22</v>
       </c>
       <c r="E134" s="4">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F134" s="4">
-        <v>5892.96</v>
+        <v>16516.97</v>
       </c>
       <c r="G134" s="4">
-        <v>0</v>
+        <v>50184.04</v>
       </c>
       <c r="H134" s="4">
-        <v>0</v>
+        <v>50184.04</v>
       </c>
       <c r="I134" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4">
-        <v>3453.12</v>
+        <v>2146.84</v>
       </c>
       <c r="K134" s="4">
-        <v>0</v>
+        <v>1952.88</v>
       </c>
       <c r="L134" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M134" s="4">
-        <v>41813.2</v>
+        <v>39986.15</v>
       </c>
       <c r="N134" s="4">
-        <v>0</v>
+        <v>124162.42</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -6662,43 +6698,43 @@
         <v>145</v>
       </c>
       <c r="B135" s="4">
-        <v>1303.849583333333</v>
+        <v>2242.025222222223</v>
       </c>
       <c r="C135" s="4">
-        <v>1741.25</v>
+        <v>2733.85</v>
       </c>
       <c r="D135" s="4">
-        <v>1916.16</v>
+        <v>2980.6</v>
       </c>
       <c r="E135" s="4">
-        <v>11622.65125</v>
+        <v>15817.99143888889</v>
       </c>
       <c r="F135" s="4">
-        <v>12201.25</v>
+        <v>20139.7</v>
       </c>
       <c r="G135" s="4">
-        <v>14710.02</v>
+        <v>18378.84</v>
       </c>
       <c r="H135" s="4">
-        <v>14710.02</v>
+        <v>18378.84</v>
       </c>
       <c r="I135" s="4">
-        <v>6764.703888888888</v>
+        <v>9337.742716666673</v>
       </c>
       <c r="J135" s="4">
-        <v>7096.25</v>
+        <v>11398.4</v>
       </c>
       <c r="K135" s="4">
-        <v>8239.469999999999</v>
+        <v>10154.23</v>
       </c>
       <c r="L135" s="4">
-        <v>41212.08666666666</v>
+        <v>72899.35422222236</v>
       </c>
       <c r="M135" s="4">
-        <v>53216.75</v>
+        <v>86587.2</v>
       </c>
       <c r="N135" s="4">
-        <v>52893.88</v>
+        <v>89497.60000000001</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -6706,43 +6742,43 @@
         <v>146</v>
       </c>
       <c r="B136" s="5">
-        <v>4346.165277777777</v>
+        <v>0</v>
       </c>
       <c r="C136" s="5">
-        <v>201.7016495227504</v>
+        <v>509.3719140690503</v>
       </c>
       <c r="D136" s="5">
-        <v>0</v>
+        <v>664.9859444023024</v>
       </c>
       <c r="E136" s="5">
-        <v>7264.157031249998</v>
+        <v>0</v>
       </c>
       <c r="F136" s="5">
-        <v>207.047901224512</v>
+        <v>121.9333812436543</v>
       </c>
       <c r="G136" s="5">
-        <v>0</v>
+        <v>36.62287850878486</v>
       </c>
       <c r="H136" s="5">
-        <v>0</v>
+        <v>36.62287850878486</v>
       </c>
       <c r="I136" s="5">
-        <v>5637.253240740741</v>
+        <v>0</v>
       </c>
       <c r="J136" s="5">
-        <v>205.5025600037068</v>
+        <v>530.9384956494196</v>
       </c>
       <c r="K136" s="5">
-        <v>0</v>
+        <v>519.961800008193</v>
       </c>
       <c r="L136" s="5">
-        <v>13737.36222222222</v>
+        <v>0</v>
       </c>
       <c r="M136" s="5">
-        <v>127.2726076932643</v>
+        <v>216.5429780061346</v>
       </c>
       <c r="N136" s="5">
-        <v>0</v>
+        <v>72.08106929616869</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -6800,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="4">
-        <v>0</v>
+        <v>218.25</v>
       </c>
       <c r="E138" s="4">
         <v>0</v>
@@ -6809,10 +6845,10 @@
         <v>0</v>
       </c>
       <c r="G138" s="4">
-        <v>665.61</v>
+        <v>436.25</v>
       </c>
       <c r="H138" s="4">
-        <v>665.61</v>
+        <v>436.25</v>
       </c>
       <c r="I138" s="4">
         <v>0</v>
@@ -6821,16 +6857,16 @@
         <v>0</v>
       </c>
       <c r="K138" s="4">
-        <v>418.93</v>
+        <v>218</v>
       </c>
       <c r="L138" s="4">
-        <v>0</v>
+        <v>716.1311111111111</v>
       </c>
       <c r="M138" s="4">
         <v>0</v>
       </c>
       <c r="N138" s="4">
-        <v>7026.51</v>
+        <v>3672.26</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -6882,43 +6918,43 @@
         <v>150</v>
       </c>
       <c r="B140" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C140" s="4">
-        <v>0</v>
+        <v>863.28</v>
       </c>
       <c r="D140" s="4">
-        <v>0</v>
+        <v>408.26</v>
       </c>
       <c r="E140" s="4">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F140" s="4">
-        <v>0</v>
+        <v>5892.96</v>
       </c>
       <c r="G140" s="4">
-        <v>0</v>
+        <v>42829.54</v>
       </c>
       <c r="H140" s="4">
-        <v>0</v>
+        <v>42829.54</v>
       </c>
       <c r="I140" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J140" s="4">
-        <v>0</v>
+        <v>3453.12</v>
       </c>
       <c r="K140" s="4">
-        <v>0</v>
+        <v>3033.04</v>
       </c>
       <c r="L140" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M140" s="4">
-        <v>0</v>
+        <v>41813.2</v>
       </c>
       <c r="N140" s="4">
-        <v>0</v>
+        <v>127035.91</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -6926,43 +6962,43 @@
         <v>151</v>
       </c>
       <c r="B141" s="4">
-        <v>775.7943972222222</v>
+        <v>1303.849583333333</v>
       </c>
       <c r="C141" s="4">
-        <v>659.78</v>
+        <v>1741.25</v>
       </c>
       <c r="D141" s="4">
-        <v>404.98</v>
+        <v>1916.16</v>
       </c>
       <c r="E141" s="4">
-        <v>5330.314783333333</v>
+        <v>11622.65125000001</v>
       </c>
       <c r="F141" s="4">
-        <v>5114.06</v>
+        <v>12201.25</v>
       </c>
       <c r="G141" s="4">
-        <v>2440.43</v>
+        <v>14710.02</v>
       </c>
       <c r="H141" s="4">
-        <v>2440.43</v>
+        <v>14710.02</v>
       </c>
       <c r="I141" s="4">
-        <v>3050.091611111111</v>
+        <v>6764.703888888889</v>
       </c>
       <c r="J141" s="4">
-        <v>2992.6</v>
+        <v>7096.25</v>
       </c>
       <c r="K141" s="4">
-        <v>1332.45</v>
+        <v>8239.469999999999</v>
       </c>
       <c r="L141" s="4">
-        <v>48049.73275833334</v>
+        <v>41212.08666666666</v>
       </c>
       <c r="M141" s="4">
-        <v>47346.1</v>
+        <v>53216.75</v>
       </c>
       <c r="N141" s="4">
-        <v>22955.67</v>
+        <v>52893.88</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -6970,43 +7006,43 @@
         <v>152</v>
       </c>
       <c r="B142" s="5">
-        <v>0</v>
+        <v>4346.165277777778</v>
       </c>
       <c r="C142" s="5">
-        <v>0</v>
+        <v>201.7016495227504</v>
       </c>
       <c r="D142" s="5">
-        <v>0</v>
+        <v>469.3479645324058</v>
       </c>
       <c r="E142" s="5">
-        <v>0</v>
+        <v>7264.157031250005</v>
       </c>
       <c r="F142" s="5">
-        <v>0</v>
+        <v>207.047901224512</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>34.34550079221024</v>
       </c>
       <c r="H142" s="5">
-        <v>0</v>
+        <v>34.34550079221024</v>
       </c>
       <c r="I142" s="5">
-        <v>0</v>
+        <v>5637.253240740742</v>
       </c>
       <c r="J142" s="5">
-        <v>0</v>
+        <v>205.5025600037068</v>
       </c>
       <c r="K142" s="5">
-        <v>0</v>
+        <v>271.6571492627858</v>
       </c>
       <c r="L142" s="5">
-        <v>0</v>
+        <v>13737.36222222222</v>
       </c>
       <c r="M142" s="5">
-        <v>0</v>
+        <v>127.2726076932643</v>
       </c>
       <c r="N142" s="5">
-        <v>0</v>
+        <v>41.63695131557683</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -7026,13 +7062,13 @@
         <v>0</v>
       </c>
       <c r="F143" s="4">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G143" s="4">
-        <v>0</v>
+        <v>17508.17</v>
       </c>
       <c r="H143" s="4">
-        <v>0</v>
+        <v>17508.17</v>
       </c>
       <c r="I143" s="4">
         <v>0</v>
@@ -7041,16 +7077,16 @@
         <v>0</v>
       </c>
       <c r="K143" s="4">
-        <v>0</v>
+        <v>17508.17</v>
       </c>
       <c r="L143" s="4">
         <v>0</v>
       </c>
       <c r="M143" s="4">
-        <v>0</v>
+        <v>7927</v>
       </c>
       <c r="N143" s="4">
-        <v>0</v>
+        <v>21475.45</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -7058,43 +7094,43 @@
         <v>154</v>
       </c>
       <c r="B144" s="4">
-        <v>725.3177777777778</v>
+        <v>0</v>
       </c>
       <c r="C144" s="4">
-        <v>663.14</v>
+        <v>0</v>
       </c>
       <c r="D144" s="4">
-        <v>505.5</v>
+        <v>0</v>
       </c>
       <c r="E144" s="4">
-        <v>5459.983633333333</v>
+        <v>0</v>
       </c>
       <c r="F144" s="4">
-        <v>5147.08</v>
+        <v>0</v>
       </c>
       <c r="G144" s="4">
-        <v>4166.2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="4">
-        <v>4166.2</v>
+        <v>0</v>
       </c>
       <c r="I144" s="4">
-        <v>2991.951633333333</v>
+        <v>0</v>
       </c>
       <c r="J144" s="4">
-        <v>2886.6</v>
+        <v>0</v>
       </c>
       <c r="K144" s="4">
-        <v>2519.41</v>
+        <v>0</v>
       </c>
       <c r="L144" s="4">
-        <v>46493.47211666666</v>
+        <v>0</v>
       </c>
       <c r="M144" s="4">
-        <v>45890</v>
+        <v>0</v>
       </c>
       <c r="N144" s="4">
-        <v>35028.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -7190,43 +7226,43 @@
         <v>157</v>
       </c>
       <c r="B147" s="4">
-        <v>999.45</v>
+        <v>0</v>
       </c>
       <c r="C147" s="4">
-        <v>1180.41</v>
+        <v>0</v>
       </c>
       <c r="D147" s="4">
-        <v>1142.01</v>
+        <v>0</v>
       </c>
       <c r="E147" s="4">
-        <v>6996.15</v>
+        <v>0</v>
       </c>
       <c r="F147" s="4">
-        <v>8662.870000000001</v>
+        <v>0</v>
       </c>
       <c r="G147" s="4">
-        <v>7994.07</v>
+        <v>665.61</v>
       </c>
       <c r="H147" s="4">
-        <v>7994.07</v>
+        <v>665.61</v>
       </c>
       <c r="I147" s="4">
-        <v>3997.8</v>
+        <v>0</v>
       </c>
       <c r="J147" s="4">
-        <v>4881.64</v>
+        <v>0</v>
       </c>
       <c r="K147" s="4">
-        <v>4568.04</v>
+        <v>418.93</v>
       </c>
       <c r="L147" s="4">
-        <v>64964.25</v>
+        <v>0</v>
       </c>
       <c r="M147" s="4">
-        <v>80326.64999999999</v>
+        <v>0</v>
       </c>
       <c r="N147" s="4">
-        <v>73300.56</v>
+        <v>7026.51</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -7293,10 +7329,10 @@
         <v>0</v>
       </c>
       <c r="G149" s="4">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H149" s="4">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I149" s="4">
         <v>0</v>
@@ -7314,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="N149" s="4">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -7322,43 +7358,43 @@
         <v>160</v>
       </c>
       <c r="B150" s="4">
-        <v>427.855</v>
+        <v>775.7943972222222</v>
       </c>
       <c r="C150" s="4">
-        <v>823.71</v>
+        <v>659.78</v>
       </c>
       <c r="D150" s="4">
-        <v>832.16</v>
+        <v>404.98</v>
       </c>
       <c r="E150" s="4">
-        <v>3145.723194444444</v>
+        <v>5330.314783333333</v>
       </c>
       <c r="F150" s="4">
-        <v>5645.97</v>
+        <v>5114.06</v>
       </c>
       <c r="G150" s="4">
-        <v>4700.38</v>
+        <v>2440.43</v>
       </c>
       <c r="H150" s="4">
-        <v>4700.38</v>
+        <v>2440.43</v>
       </c>
       <c r="I150" s="4">
-        <v>1771.448888888889</v>
+        <v>3050.091611111111</v>
       </c>
       <c r="J150" s="4">
-        <v>2880.44</v>
+        <v>2992.6</v>
       </c>
       <c r="K150" s="4">
-        <v>2609.89</v>
+        <v>1332.45</v>
       </c>
       <c r="L150" s="4">
-        <v>27664.99833333334</v>
+        <v>48049.73275833334</v>
       </c>
       <c r="M150" s="4">
-        <v>52461.15</v>
+        <v>47346.1</v>
       </c>
       <c r="N150" s="4">
-        <v>42992.56</v>
+        <v>22955.67</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -7381,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="G151" s="5">
-        <v>0</v>
+        <v>61.01074999999999</v>
       </c>
       <c r="H151" s="5">
-        <v>0</v>
+        <v>61.01074999999999</v>
       </c>
       <c r="I151" s="5">
         <v>0</v>
@@ -7402,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5">
-        <v>0</v>
+        <v>286.945875</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -7413,40 +7449,40 @@
         <v>0</v>
       </c>
       <c r="C152" s="4">
-        <v>0</v>
+        <v>321.12</v>
       </c>
       <c r="D152" s="4">
-        <v>0</v>
+        <v>2485.95</v>
       </c>
       <c r="E152" s="4">
         <v>0</v>
       </c>
       <c r="F152" s="4">
-        <v>0</v>
+        <v>2247.84</v>
       </c>
       <c r="G152" s="4">
-        <v>0</v>
+        <v>29562.99</v>
       </c>
       <c r="H152" s="4">
-        <v>0</v>
+        <v>29562.99</v>
       </c>
       <c r="I152" s="4">
         <v>0</v>
       </c>
       <c r="J152" s="4">
-        <v>0</v>
+        <v>1284.48</v>
       </c>
       <c r="K152" s="4">
-        <v>0</v>
+        <v>6420.69</v>
       </c>
       <c r="L152" s="4">
         <v>0</v>
       </c>
       <c r="M152" s="4">
-        <v>0</v>
+        <v>20872.8</v>
       </c>
       <c r="N152" s="4">
-        <v>0</v>
+        <v>107184.63</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -7454,43 +7490,43 @@
         <v>163</v>
       </c>
       <c r="B153" s="4">
-        <v>398.52</v>
+        <v>0</v>
       </c>
       <c r="C153" s="4">
-        <v>227.21</v>
+        <v>0</v>
       </c>
       <c r="D153" s="4">
-        <v>225.28</v>
+        <v>0</v>
       </c>
       <c r="E153" s="4">
-        <v>2789.64</v>
+        <v>0</v>
       </c>
       <c r="F153" s="4">
-        <v>1590.47</v>
+        <v>0</v>
       </c>
       <c r="G153" s="4">
-        <v>1576.96</v>
+        <v>0</v>
       </c>
       <c r="H153" s="4">
-        <v>1576.96</v>
+        <v>0</v>
       </c>
       <c r="I153" s="4">
-        <v>1594.08</v>
+        <v>0</v>
       </c>
       <c r="J153" s="4">
-        <v>908.84</v>
+        <v>0</v>
       </c>
       <c r="K153" s="4">
-        <v>901.12</v>
+        <v>0</v>
       </c>
       <c r="L153" s="4">
-        <v>25903.8</v>
+        <v>0</v>
       </c>
       <c r="M153" s="4">
-        <v>14768.65</v>
+        <v>0</v>
       </c>
       <c r="N153" s="4">
-        <v>12705.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -7586,43 +7622,43 @@
         <v>166</v>
       </c>
       <c r="B156" s="4">
-        <v>853.1783</v>
+        <v>725.3177777777778</v>
       </c>
       <c r="C156" s="4">
-        <v>693.0599999999999</v>
+        <v>663.14</v>
       </c>
       <c r="D156" s="4">
-        <v>325.71</v>
+        <v>505.5</v>
       </c>
       <c r="E156" s="4">
-        <v>5645.336686111112</v>
+        <v>5459.983633333333</v>
       </c>
       <c r="F156" s="4">
-        <v>5634.22</v>
+        <v>5147.08</v>
       </c>
       <c r="G156" s="4">
-        <v>1985.19</v>
+        <v>4166.2</v>
       </c>
       <c r="H156" s="4">
-        <v>1985.19</v>
+        <v>4166.2</v>
       </c>
       <c r="I156" s="4">
-        <v>3087.894688888889</v>
+        <v>2991.951633333333</v>
       </c>
       <c r="J156" s="4">
-        <v>3085.36</v>
+        <v>2886.6</v>
       </c>
       <c r="K156" s="4">
-        <v>1011.1</v>
+        <v>2519.41</v>
       </c>
       <c r="L156" s="4">
-        <v>52370.23198055556</v>
+        <v>46493.47211666666</v>
       </c>
       <c r="M156" s="4">
-        <v>52094.1</v>
+        <v>45890</v>
       </c>
       <c r="N156" s="4">
-        <v>17633.46</v>
+        <v>35028.47</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -7718,43 +7754,43 @@
         <v>169</v>
       </c>
       <c r="B159" s="4">
-        <v>175.48</v>
+        <v>999.45</v>
       </c>
       <c r="C159" s="4">
-        <v>0</v>
+        <v>1180.41</v>
       </c>
       <c r="D159" s="4">
-        <v>0</v>
+        <v>1142.01</v>
       </c>
       <c r="E159" s="4">
-        <v>1228.36</v>
+        <v>6996.15</v>
       </c>
       <c r="F159" s="4">
-        <v>0</v>
+        <v>8662.870000000001</v>
       </c>
       <c r="G159" s="4">
-        <v>0</v>
+        <v>7994.07</v>
       </c>
       <c r="H159" s="4">
-        <v>0</v>
+        <v>7994.07</v>
       </c>
       <c r="I159" s="4">
-        <v>701.92</v>
+        <v>3997.8</v>
       </c>
       <c r="J159" s="4">
-        <v>0</v>
+        <v>4881.64</v>
       </c>
       <c r="K159" s="4">
-        <v>0</v>
+        <v>4568.04</v>
       </c>
       <c r="L159" s="4">
-        <v>11406.2</v>
+        <v>64964.25</v>
       </c>
       <c r="M159" s="4">
-        <v>0</v>
+        <v>80326.64999999999</v>
       </c>
       <c r="N159" s="4">
-        <v>0</v>
+        <v>73300.56</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -7850,43 +7886,43 @@
         <v>172</v>
       </c>
       <c r="B162" s="4">
-        <v>0</v>
+        <v>427.855</v>
       </c>
       <c r="C162" s="4">
-        <v>0</v>
+        <v>823.71</v>
       </c>
       <c r="D162" s="4">
-        <v>0</v>
+        <v>832.16</v>
       </c>
       <c r="E162" s="4">
-        <v>292.3</v>
+        <v>3145.723194444445</v>
       </c>
       <c r="F162" s="4">
-        <v>0</v>
+        <v>5645.97</v>
       </c>
       <c r="G162" s="4">
-        <v>0</v>
+        <v>4700.38</v>
       </c>
       <c r="H162" s="4">
-        <v>0</v>
+        <v>4700.38</v>
       </c>
       <c r="I162" s="4">
-        <v>138.67</v>
+        <v>1771.448888888889</v>
       </c>
       <c r="J162" s="4">
-        <v>0</v>
+        <v>2880.44</v>
       </c>
       <c r="K162" s="4">
-        <v>0</v>
+        <v>2609.89</v>
       </c>
       <c r="L162" s="4">
-        <v>418.925</v>
+        <v>27664.99833333334</v>
       </c>
       <c r="M162" s="4">
-        <v>0</v>
+        <v>52461.15</v>
       </c>
       <c r="N162" s="4">
-        <v>0</v>
+        <v>42992.56</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -7982,43 +8018,43 @@
         <v>175</v>
       </c>
       <c r="B165" s="4">
-        <v>0</v>
+        <v>398.52</v>
       </c>
       <c r="C165" s="4">
-        <v>0</v>
+        <v>227.21</v>
       </c>
       <c r="D165" s="4">
-        <v>0</v>
+        <v>225.28</v>
       </c>
       <c r="E165" s="4">
-        <v>95.93000000000001</v>
+        <v>2789.64</v>
       </c>
       <c r="F165" s="4">
-        <v>0</v>
+        <v>1590.47</v>
       </c>
       <c r="G165" s="4">
-        <v>0</v>
+        <v>1576.96</v>
       </c>
       <c r="H165" s="4">
-        <v>0</v>
+        <v>1576.96</v>
       </c>
       <c r="I165" s="4">
-        <v>95.93000000000001</v>
+        <v>1594.08</v>
       </c>
       <c r="J165" s="4">
-        <v>0</v>
+        <v>908.84</v>
       </c>
       <c r="K165" s="4">
-        <v>0</v>
+        <v>901.12</v>
       </c>
       <c r="L165" s="4">
-        <v>203.83</v>
+        <v>25903.8</v>
       </c>
       <c r="M165" s="4">
-        <v>0</v>
+        <v>14768.65</v>
       </c>
       <c r="N165" s="4">
-        <v>228.24</v>
+        <v>12705.62</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -8065,180 +8101,708 @@
         <v>0</v>
       </c>
     </row>
+    <row r="167" spans="1:14">
+      <c r="A167" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B167" s="4">
+        <v>0</v>
+      </c>
+      <c r="C167" s="4">
+        <v>0</v>
+      </c>
+      <c r="D167" s="4">
+        <v>0</v>
+      </c>
+      <c r="E167" s="4">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4">
+        <v>0</v>
+      </c>
+      <c r="G167" s="4">
+        <v>0</v>
+      </c>
+      <c r="H167" s="4">
+        <v>0</v>
+      </c>
+      <c r="I167" s="4">
+        <v>0</v>
+      </c>
+      <c r="J167" s="4">
+        <v>0</v>
+      </c>
+      <c r="K167" s="4">
+        <v>0</v>
+      </c>
+      <c r="L167" s="4">
+        <v>0</v>
+      </c>
+      <c r="M167" s="4">
+        <v>0</v>
+      </c>
+      <c r="N167" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="A168" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" s="4">
+        <v>853.1783</v>
+      </c>
+      <c r="C168" s="4">
+        <v>693.0599999999999</v>
+      </c>
+      <c r="D168" s="4">
+        <v>325.71</v>
+      </c>
+      <c r="E168" s="4">
+        <v>5645.336686111112</v>
+      </c>
+      <c r="F168" s="4">
+        <v>5634.22</v>
+      </c>
+      <c r="G168" s="4">
+        <v>1985.19</v>
+      </c>
+      <c r="H168" s="4">
+        <v>1985.19</v>
+      </c>
+      <c r="I168" s="4">
+        <v>3087.894688888889</v>
+      </c>
+      <c r="J168" s="4">
+        <v>3085.36</v>
+      </c>
+      <c r="K168" s="4">
+        <v>1011.1</v>
+      </c>
+      <c r="L168" s="4">
+        <v>52370.23198055556</v>
+      </c>
+      <c r="M168" s="4">
+        <v>52094.1</v>
+      </c>
+      <c r="N168" s="4">
+        <v>17633.46</v>
+      </c>
+    </row>
     <row r="169" spans="1:14">
-      <c r="A169" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B169" s="4">
+      <c r="A169" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B169" s="5">
+        <v>0</v>
+      </c>
+      <c r="C169" s="5">
+        <v>0</v>
+      </c>
+      <c r="D169" s="5">
+        <v>0</v>
+      </c>
+      <c r="E169" s="5">
+        <v>0</v>
+      </c>
+      <c r="F169" s="5">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5">
+        <v>0</v>
+      </c>
+      <c r="H169" s="5">
+        <v>0</v>
+      </c>
+      <c r="I169" s="5">
+        <v>0</v>
+      </c>
+      <c r="J169" s="5">
+        <v>0</v>
+      </c>
+      <c r="K169" s="5">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5">
+        <v>0</v>
+      </c>
+      <c r="M169" s="5">
+        <v>0</v>
+      </c>
+      <c r="N169" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="A170" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B170" s="4">
+        <v>0</v>
+      </c>
+      <c r="C170" s="4">
+        <v>0</v>
+      </c>
+      <c r="D170" s="4">
+        <v>0</v>
+      </c>
+      <c r="E170" s="4">
+        <v>0</v>
+      </c>
+      <c r="F170" s="4">
+        <v>0</v>
+      </c>
+      <c r="G170" s="4">
+        <v>0</v>
+      </c>
+      <c r="H170" s="4">
+        <v>0</v>
+      </c>
+      <c r="I170" s="4">
+        <v>0</v>
+      </c>
+      <c r="J170" s="4">
+        <v>0</v>
+      </c>
+      <c r="K170" s="4">
+        <v>0</v>
+      </c>
+      <c r="L170" s="4">
+        <v>0</v>
+      </c>
+      <c r="M170" s="4">
+        <v>0</v>
+      </c>
+      <c r="N170" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14">
+      <c r="A171" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B171" s="4">
+        <v>175.48</v>
+      </c>
+      <c r="C171" s="4">
+        <v>0</v>
+      </c>
+      <c r="D171" s="4">
+        <v>0</v>
+      </c>
+      <c r="E171" s="4">
+        <v>1228.36</v>
+      </c>
+      <c r="F171" s="4">
+        <v>0</v>
+      </c>
+      <c r="G171" s="4">
+        <v>0</v>
+      </c>
+      <c r="H171" s="4">
+        <v>0</v>
+      </c>
+      <c r="I171" s="4">
+        <v>701.92</v>
+      </c>
+      <c r="J171" s="4">
+        <v>0</v>
+      </c>
+      <c r="K171" s="4">
+        <v>0</v>
+      </c>
+      <c r="L171" s="4">
+        <v>11406.2</v>
+      </c>
+      <c r="M171" s="4">
+        <v>0</v>
+      </c>
+      <c r="N171" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14">
+      <c r="A172" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B172" s="5">
+        <v>0</v>
+      </c>
+      <c r="C172" s="5">
+        <v>0</v>
+      </c>
+      <c r="D172" s="5">
+        <v>0</v>
+      </c>
+      <c r="E172" s="5">
+        <v>0</v>
+      </c>
+      <c r="F172" s="5">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5">
+        <v>0</v>
+      </c>
+      <c r="H172" s="5">
+        <v>0</v>
+      </c>
+      <c r="I172" s="5">
+        <v>0</v>
+      </c>
+      <c r="J172" s="5">
+        <v>0</v>
+      </c>
+      <c r="K172" s="5">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5">
+        <v>0</v>
+      </c>
+      <c r="M172" s="5">
+        <v>0</v>
+      </c>
+      <c r="N172" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" s="4">
+        <v>0</v>
+      </c>
+      <c r="C173" s="4">
+        <v>0</v>
+      </c>
+      <c r="D173" s="4">
+        <v>0</v>
+      </c>
+      <c r="E173" s="4">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4">
+        <v>0</v>
+      </c>
+      <c r="G173" s="4">
+        <v>0</v>
+      </c>
+      <c r="H173" s="4">
+        <v>0</v>
+      </c>
+      <c r="I173" s="4">
+        <v>0</v>
+      </c>
+      <c r="J173" s="4">
+        <v>0</v>
+      </c>
+      <c r="K173" s="4">
+        <v>0</v>
+      </c>
+      <c r="L173" s="4">
+        <v>0</v>
+      </c>
+      <c r="M173" s="4">
+        <v>0</v>
+      </c>
+      <c r="N173" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14">
+      <c r="A174" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" s="4">
+        <v>0</v>
+      </c>
+      <c r="C174" s="4">
+        <v>0</v>
+      </c>
+      <c r="D174" s="4">
+        <v>0</v>
+      </c>
+      <c r="E174" s="4">
+        <v>292.3</v>
+      </c>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="4">
+        <v>0</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0</v>
+      </c>
+      <c r="I174" s="4">
+        <v>138.67</v>
+      </c>
+      <c r="J174" s="4">
+        <v>0</v>
+      </c>
+      <c r="K174" s="4">
+        <v>0</v>
+      </c>
+      <c r="L174" s="4">
+        <v>418.925</v>
+      </c>
+      <c r="M174" s="4">
+        <v>0</v>
+      </c>
+      <c r="N174" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" s="5">
+        <v>0</v>
+      </c>
+      <c r="C175" s="5">
+        <v>0</v>
+      </c>
+      <c r="D175" s="5">
+        <v>0</v>
+      </c>
+      <c r="E175" s="5">
+        <v>0</v>
+      </c>
+      <c r="F175" s="5">
+        <v>0</v>
+      </c>
+      <c r="G175" s="5">
+        <v>0</v>
+      </c>
+      <c r="H175" s="5">
+        <v>0</v>
+      </c>
+      <c r="I175" s="5">
+        <v>0</v>
+      </c>
+      <c r="J175" s="5">
+        <v>0</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>0</v>
+      </c>
+      <c r="M175" s="5">
+        <v>0</v>
+      </c>
+      <c r="N175" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="A176" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B176" s="4">
+        <v>0</v>
+      </c>
+      <c r="C176" s="4">
+        <v>0</v>
+      </c>
+      <c r="D176" s="4">
+        <v>0</v>
+      </c>
+      <c r="E176" s="4">
+        <v>0</v>
+      </c>
+      <c r="F176" s="4">
+        <v>0</v>
+      </c>
+      <c r="G176" s="4">
+        <v>682.0700000000001</v>
+      </c>
+      <c r="H176" s="4">
+        <v>682.0700000000001</v>
+      </c>
+      <c r="I176" s="4">
+        <v>0</v>
+      </c>
+      <c r="J176" s="4">
+        <v>0</v>
+      </c>
+      <c r="K176" s="4">
+        <v>0</v>
+      </c>
+      <c r="L176" s="4">
+        <v>0</v>
+      </c>
+      <c r="M176" s="4">
+        <v>0</v>
+      </c>
+      <c r="N176" s="4">
+        <v>1364.14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14">
+      <c r="A177" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B177" s="4">
+        <v>0</v>
+      </c>
+      <c r="C177" s="4">
+        <v>0</v>
+      </c>
+      <c r="D177" s="4">
+        <v>0</v>
+      </c>
+      <c r="E177" s="4">
+        <v>95.93000000000001</v>
+      </c>
+      <c r="F177" s="4">
+        <v>0</v>
+      </c>
+      <c r="G177" s="4">
+        <v>0</v>
+      </c>
+      <c r="H177" s="4">
+        <v>0</v>
+      </c>
+      <c r="I177" s="4">
+        <v>95.93000000000001</v>
+      </c>
+      <c r="J177" s="4">
+        <v>0</v>
+      </c>
+      <c r="K177" s="4">
+        <v>0</v>
+      </c>
+      <c r="L177" s="4">
+        <v>203.83</v>
+      </c>
+      <c r="M177" s="4">
+        <v>0</v>
+      </c>
+      <c r="N177" s="4">
+        <v>228.24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
+      <c r="A178" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B178" s="5">
+        <v>0</v>
+      </c>
+      <c r="C178" s="5">
+        <v>0</v>
+      </c>
+      <c r="D178" s="5">
+        <v>0</v>
+      </c>
+      <c r="E178" s="5">
+        <v>0</v>
+      </c>
+      <c r="F178" s="5">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5">
+        <v>0</v>
+      </c>
+      <c r="H178" s="5">
+        <v>0</v>
+      </c>
+      <c r="I178" s="5">
+        <v>0</v>
+      </c>
+      <c r="J178" s="5">
+        <v>0</v>
+      </c>
+      <c r="K178" s="5">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5">
+        <v>0</v>
+      </c>
+      <c r="M178" s="5">
+        <v>0</v>
+      </c>
+      <c r="N178" s="5">
+        <v>16.73142052868474</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B181" s="4">
         <v>209568.09</v>
       </c>
-      <c r="C169" s="4">
-        <v>475532.5000000001</v>
-      </c>
-      <c r="D169" s="4">
-        <v>251726.8</v>
-      </c>
-      <c r="E169" s="4">
+      <c r="C181" s="4">
+        <v>515872.14</v>
+      </c>
+      <c r="D181" s="4">
+        <v>413401.0800000001</v>
+      </c>
+      <c r="E181" s="4">
         <v>2678996.35</v>
       </c>
-      <c r="F169" s="4">
-        <v>4744626.369999999</v>
-      </c>
-      <c r="G169" s="4">
-        <v>2972367.539999999</v>
-      </c>
-      <c r="H169" s="4">
-        <v>2972367.539999999</v>
-      </c>
-      <c r="I169" s="4">
+      <c r="F181" s="4">
+        <v>5221686.37</v>
+      </c>
+      <c r="G181" s="4">
+        <v>5278449.32</v>
+      </c>
+      <c r="H181" s="4">
+        <v>5278449.32</v>
+      </c>
+      <c r="I181" s="4">
         <v>1316093.55</v>
       </c>
-      <c r="J169" s="4">
-        <v>2306886.29</v>
-      </c>
-      <c r="K169" s="4">
-        <v>1679661.323</v>
-      </c>
-      <c r="L169" s="4">
+      <c r="J181" s="4">
+        <v>2489623</v>
+      </c>
+      <c r="K181" s="4">
+        <v>2368614.56</v>
+      </c>
+      <c r="L181" s="4">
         <v>5404628.700000001</v>
       </c>
-      <c r="M169" s="4">
-        <v>11823621.15</v>
-      </c>
-      <c r="N169" s="4">
-        <v>6814842.639999998</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14">
-      <c r="A170" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B170" s="4">
-        <v>46053.83888055555</v>
-      </c>
-      <c r="C170" s="4">
+      <c r="M181" s="4">
+        <v>12719297.67</v>
+      </c>
+      <c r="N181" s="4">
+        <v>12345684.98</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
+      <c r="A182" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B182" s="4">
+        <v>47099.24881111111</v>
+      </c>
+      <c r="C182" s="4">
         <v>57187.49000000001</v>
       </c>
-      <c r="D170" s="4">
+      <c r="D182" s="4">
         <v>57016.36000000001</v>
       </c>
-      <c r="E170" s="4">
-        <v>377286.6267444445</v>
-      </c>
-      <c r="F170" s="4">
+      <c r="E182" s="4">
+        <v>378332.0366750001</v>
+      </c>
+      <c r="F182" s="4">
         <v>457355.8299999999</v>
       </c>
-      <c r="G170" s="4">
+      <c r="G182" s="4">
         <v>423908.11</v>
       </c>
-      <c r="H170" s="4">
+      <c r="H182" s="4">
         <v>423908.11</v>
       </c>
-      <c r="I170" s="4">
-        <v>203284.4329166666</v>
-      </c>
-      <c r="J170" s="4">
+      <c r="I182" s="4">
+        <v>204329.8428472222</v>
+      </c>
+      <c r="J182" s="4">
         <v>248534.57</v>
       </c>
-      <c r="K170" s="4">
+      <c r="K182" s="4">
         <v>245564.4200000002</v>
       </c>
-      <c r="L170" s="4">
-        <v>2334196.591638889</v>
-      </c>
-      <c r="M170" s="4">
+      <c r="L182" s="4">
+        <v>2334870.657125</v>
+      </c>
+      <c r="M182" s="4">
         <v>2595382.99</v>
       </c>
-      <c r="N170" s="4">
+      <c r="N182" s="4">
         <v>2551113.72</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
-      <c r="A171" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B171" s="5">
-        <v>21.97559699120011</v>
-      </c>
-      <c r="C171" s="5">
-        <v>12.02598981142193</v>
-      </c>
-      <c r="D171" s="5">
-        <v>22.65009526200627</v>
-      </c>
-      <c r="E171" s="5">
-        <v>14.08313328774951</v>
-      </c>
-      <c r="F171" s="5">
-        <v>9.639448806587483</v>
-      </c>
-      <c r="G171" s="5">
-        <v>14.26163165541769</v>
-      </c>
-      <c r="H171" s="5">
-        <v>14.26163165541769</v>
-      </c>
-      <c r="I171" s="5">
-        <v>15.44604735101594</v>
-      </c>
-      <c r="J171" s="5">
-        <v>10.77359430663572</v>
-      </c>
-      <c r="K171" s="5">
-        <v>14.61987703338932</v>
-      </c>
-      <c r="L171" s="5">
-        <v>43.18884277173174</v>
-      </c>
-      <c r="M171" s="5">
-        <v>21.95083009742747</v>
-      </c>
-      <c r="N171" s="5">
-        <v>37.43466804392714</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14">
-      <c r="A172" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B172" s="4">
-        <v>163514.2511194445</v>
-      </c>
-      <c r="C172" s="4">
-        <v>418345.0100000001</v>
-      </c>
-      <c r="D172" s="4">
-        <v>194710.44</v>
-      </c>
-      <c r="E172" s="4">
-        <v>2301709.723255556</v>
-      </c>
-      <c r="F172" s="4">
-        <v>4287270.539999999</v>
-      </c>
-      <c r="G172" s="4">
-        <v>2548459.429999999</v>
-      </c>
-      <c r="H172" s="4">
-        <v>2548459.429999999</v>
-      </c>
-      <c r="I172" s="4">
-        <v>1112809.117083333</v>
-      </c>
-      <c r="J172" s="4">
-        <v>2058351.72</v>
-      </c>
-      <c r="K172" s="4">
-        <v>1434096.903</v>
-      </c>
-      <c r="L172" s="4">
-        <v>3070432.108361112</v>
-      </c>
-      <c r="M172" s="4">
-        <v>9228238.159999998</v>
-      </c>
-      <c r="N172" s="4">
-        <v>4263728.919999998</v>
+    <row r="183" spans="1:14">
+      <c r="A183" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B183" s="5">
+        <v>22.47443721566156</v>
+      </c>
+      <c r="C183" s="5">
+        <v>11.08559380624819</v>
+      </c>
+      <c r="D183" s="5">
+        <v>13.79202008857839</v>
+      </c>
+      <c r="E183" s="5">
+        <v>14.12215573473999</v>
+      </c>
+      <c r="F183" s="5">
+        <v>8.758776333784288</v>
+      </c>
+      <c r="G183" s="5">
+        <v>8.03092128579914</v>
+      </c>
+      <c r="H183" s="5">
+        <v>8.03092128579914</v>
+      </c>
+      <c r="I183" s="5">
+        <v>15.52548014897742</v>
+      </c>
+      <c r="J183" s="5">
+        <v>9.98281948712717</v>
+      </c>
+      <c r="K183" s="5">
+        <v>10.36742845995172</v>
+      </c>
+      <c r="L183" s="5">
+        <v>43.20131477533322</v>
+      </c>
+      <c r="M183" s="5">
+        <v>20.4050809827458</v>
+      </c>
+      <c r="N183" s="5">
+        <v>20.66401114343029</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14">
+      <c r="A184" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B184" s="4">
+        <v>162468.8411888889</v>
+      </c>
+      <c r="C184" s="4">
+        <v>458684.65</v>
+      </c>
+      <c r="D184" s="4">
+        <v>356384.7200000001</v>
+      </c>
+      <c r="E184" s="4">
+        <v>2300664.313325</v>
+      </c>
+      <c r="F184" s="4">
+        <v>4764330.54</v>
+      </c>
+      <c r="G184" s="4">
+        <v>4854541.21</v>
+      </c>
+      <c r="H184" s="4">
+        <v>4854541.21</v>
+      </c>
+      <c r="I184" s="4">
+        <v>1111763.707152778</v>
+      </c>
+      <c r="J184" s="4">
+        <v>2241088.43</v>
+      </c>
+      <c r="K184" s="4">
+        <v>2123050.14</v>
+      </c>
+      <c r="L184" s="4">
+        <v>3069758.042875001</v>
+      </c>
+      <c r="M184" s="4">
+        <v>10123914.68</v>
+      </c>
+      <c r="N184" s="4">
+        <v>9794571.260000002</v>
       </c>
     </row>
   </sheetData>
